--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-05-16.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-05-16.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CB87"/>
+  <dimension ref="A1:CB80"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -857,13 +857,13 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>3.35</v>
+        <v>3.45</v>
       </c>
       <c r="G2" t="n">
         <v>4.8</v>
       </c>
       <c r="H2" t="n">
-        <v>1.83</v>
+        <v>1.92</v>
       </c>
       <c r="I2" t="n">
         <v>2.26</v>
@@ -872,7 +872,7 @@
         <v>3.35</v>
       </c>
       <c r="K2" t="n">
-        <v>5.5</v>
+        <v>5.3</v>
       </c>
       <c r="L2" t="n">
         <v>0</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-05-14 00:34:16</t>
+          <t>2026-05-14 02:53:36</t>
         </is>
       </c>
     </row>
@@ -1111,7 +1111,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>2.28</v>
+        <v>2.32</v>
       </c>
       <c r="G3" t="n">
         <v>2.4</v>
@@ -1144,7 +1144,7 @@
         <v>2.68</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="R3" t="n">
         <v>1.68</v>
@@ -1165,10 +1165,10 @@
         <v>1.71</v>
       </c>
       <c r="X3" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="Y3" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="Z3" t="n">
         <v>29</v>
@@ -1183,7 +1183,7 @@
         <v>10.5</v>
       </c>
       <c r="AD3" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AE3" t="n">
         <v>32</v>
@@ -1228,7 +1228,7 @@
         <v>21</v>
       </c>
       <c r="AS3" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="AT3" t="n">
         <v>14.5</v>
@@ -1264,7 +1264,7 @@
         <v>19</v>
       </c>
       <c r="BE3" t="n">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="BF3" t="n">
         <v>9.800000000000001</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-05-14 00:34:16</t>
+          <t>2026-05-14 02:53:36</t>
         </is>
       </c>
     </row>
@@ -1365,22 +1365,22 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1.04</v>
+        <v>1.53</v>
       </c>
       <c r="G4" t="n">
-        <v>1000</v>
+        <v>990</v>
       </c>
       <c r="H4" t="n">
         <v>1.04</v>
       </c>
       <c r="I4" t="n">
-        <v>1000</v>
+        <v>990</v>
       </c>
       <c r="J4" t="n">
         <v>1.04</v>
       </c>
       <c r="K4" t="n">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="L4" t="n">
         <v>1.01</v>
@@ -1389,7 +1389,7 @@
         <v>1.01</v>
       </c>
       <c r="N4" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="O4" t="n">
         <v>1.01</v>
@@ -1398,7 +1398,7 @@
         <v>1.24</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="R4" t="n">
         <v>1.18</v>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-05-14 00:34:16</t>
+          <t>2026-05-14 02:53:36</t>
         </is>
       </c>
     </row>
@@ -1631,7 +1631,7 @@
         <v>870</v>
       </c>
       <c r="J5" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="K5" t="n">
         <v>550</v>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-05-14 00:34:16</t>
+          <t>2026-05-14 02:53:36</t>
         </is>
       </c>
     </row>
@@ -1876,16 +1876,16 @@
         <v>1.04</v>
       </c>
       <c r="G6" t="n">
-        <v>1000</v>
+        <v>750</v>
       </c>
       <c r="H6" t="n">
         <v>1.04</v>
       </c>
       <c r="I6" t="n">
-        <v>1000</v>
+        <v>850</v>
       </c>
       <c r="J6" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="K6" t="n">
         <v>390</v>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-05-14 00:34:16</t>
+          <t>2026-05-14 02:53:36</t>
         </is>
       </c>
     </row>
@@ -2130,16 +2130,16 @@
         <v>1.04</v>
       </c>
       <c r="G7" t="n">
-        <v>1000</v>
+        <v>370</v>
       </c>
       <c r="H7" t="n">
         <v>1.04</v>
       </c>
       <c r="I7" t="n">
-        <v>1000</v>
+        <v>440</v>
       </c>
       <c r="J7" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="K7" t="n">
         <v>520</v>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-05-14 00:34:16</t>
+          <t>2026-05-14 02:53:36</t>
         </is>
       </c>
     </row>
@@ -2384,16 +2384,16 @@
         <v>2.44</v>
       </c>
       <c r="G8" t="n">
-        <v>2.7</v>
+        <v>2.68</v>
       </c>
       <c r="H8" t="n">
-        <v>2.7</v>
+        <v>1.32</v>
       </c>
       <c r="I8" t="n">
         <v>3.05</v>
       </c>
       <c r="J8" t="n">
-        <v>3.55</v>
+        <v>1.48</v>
       </c>
       <c r="K8" t="n">
         <v>4.1</v>
@@ -2411,10 +2411,10 @@
         <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.71</v>
+        <v>1.6</v>
       </c>
       <c r="R8" t="n">
         <v>0</v>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-05-14 00:34:16</t>
+          <t>2026-05-14 02:53:36</t>
         </is>
       </c>
     </row>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-05-14 00:34:16</t>
+          <t>2026-05-14 02:53:36</t>
         </is>
       </c>
     </row>
@@ -3112,7 +3112,7 @@
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-05-14 00:34:16</t>
+          <t>2026-05-14 02:53:36</t>
         </is>
       </c>
     </row>
@@ -3143,7 +3143,7 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="G11" t="n">
         <v>1.68</v>
@@ -3176,7 +3176,7 @@
         <v>2.14</v>
       </c>
       <c r="Q11" t="n">
-        <v>1.65</v>
+        <v>1.71</v>
       </c>
       <c r="R11" t="n">
         <v>0</v>
@@ -3366,14 +3366,14 @@
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-05-14 00:34:16</t>
+          <t>2026-05-14 02:53:36</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Spanish Segunda Division</t>
+          <t>Chinese Super League</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -3388,239 +3388,239 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Sociedad B</t>
+          <t>Yunnan Yukun</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Mirandes</t>
+          <t>Shanghai Shenhua</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>3.25</v>
+        <v>2.08</v>
       </c>
       <c r="G12" t="n">
-        <v>3.5</v>
+        <v>2.24</v>
       </c>
       <c r="H12" t="n">
-        <v>2.16</v>
+        <v>3.1</v>
       </c>
       <c r="I12" t="n">
-        <v>2.26</v>
+        <v>3.6</v>
       </c>
       <c r="J12" t="n">
-        <v>3.85</v>
+        <v>4.2</v>
       </c>
       <c r="K12" t="n">
-        <v>4.4</v>
+        <v>5.1</v>
       </c>
       <c r="L12" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="N12" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="O12" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="P12" t="n">
-        <v>2.16</v>
+        <v>3.3</v>
       </c>
       <c r="Q12" t="n">
-        <v>1.71</v>
+        <v>1.32</v>
       </c>
       <c r="R12" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="S12" t="n">
-        <v>2.84</v>
+        <v>0</v>
       </c>
       <c r="T12" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="U12" t="n">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="V12" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="W12" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="Y12" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="Z12" t="n">
-        <v>16.5</v>
+        <v>0</v>
       </c>
       <c r="AA12" t="n">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="AB12" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="AC12" t="n">
-        <v>11.5</v>
+        <v>0</v>
       </c>
       <c r="AD12" t="n">
-        <v>11.5</v>
+        <v>0</v>
       </c>
       <c r="AE12" t="n">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="AF12" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="AG12" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="AH12" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="AI12" t="n">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="AJ12" t="n">
-        <v>65</v>
+        <v>0</v>
       </c>
       <c r="AK12" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="AL12" t="n">
-        <v>46</v>
+        <v>0</v>
       </c>
       <c r="AM12" t="n">
-        <v>95</v>
+        <v>0</v>
       </c>
       <c r="AN12" t="n">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="AO12" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="AP12" t="n">
-        <v>4.9</v>
+        <v>0</v>
       </c>
       <c r="AQ12" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="AR12" t="n">
-        <v>11.5</v>
+        <v>0</v>
       </c>
       <c r="AS12" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="AT12" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="AU12" t="n">
-        <v>8.199999999999999</v>
+        <v>0</v>
       </c>
       <c r="AV12" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="AW12" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="AX12" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AY12" t="n">
-        <v>12.5</v>
+        <v>0</v>
       </c>
       <c r="AZ12" t="n">
-        <v>14.5</v>
+        <v>0</v>
       </c>
       <c r="BA12" t="n">
-        <v>5.1</v>
+        <v>0</v>
       </c>
       <c r="BB12" t="n">
-        <v>5.6</v>
+        <v>0</v>
       </c>
       <c r="BC12" t="n">
-        <v>5.3</v>
+        <v>0</v>
       </c>
       <c r="BD12" t="n">
-        <v>5.4</v>
+        <v>0</v>
       </c>
       <c r="BE12" t="n">
-        <v>5.8</v>
+        <v>0</v>
       </c>
       <c r="BF12" t="n">
-        <v>5.2</v>
+        <v>0</v>
       </c>
       <c r="BG12" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="BH12" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="BI12" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="BJ12" t="n">
-        <v>9.199999999999999</v>
+        <v>0</v>
       </c>
       <c r="BK12" t="n">
-        <v>5.4</v>
+        <v>0</v>
       </c>
       <c r="BL12" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BM12" t="n">
-        <v>11.5</v>
+        <v>0</v>
       </c>
       <c r="BN12" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="BO12" t="n">
-        <v>5.2</v>
+        <v>0</v>
       </c>
       <c r="BP12" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BQ12" t="n">
-        <v>8.800000000000001</v>
+        <v>0</v>
       </c>
       <c r="BR12" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BS12" t="n">
-        <v>9.6</v>
+        <v>0</v>
       </c>
       <c r="BT12" t="n">
-        <v>5.3</v>
+        <v>0</v>
       </c>
       <c r="BU12" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="BV12" t="n">
-        <v>15.5</v>
+        <v>0</v>
       </c>
       <c r="BW12" t="n">
-        <v>7.2</v>
+        <v>0</v>
       </c>
       <c r="BX12" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BY12" t="n">
-        <v>8.800000000000001</v>
+        <v>0</v>
       </c>
       <c r="BZ12" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="CA12" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-05-14 00:34:16</t>
+          <t>2026-05-14 02:53:36</t>
         </is>
       </c>
     </row>
@@ -3642,31 +3642,31 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Persis Solo</t>
+          <t>Malut United</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Dewa United FC</t>
+          <t>Persita Tangerang</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>2.66</v>
+        <v>1.69</v>
       </c>
       <c r="G13" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="H13" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="I13" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="J13" t="n">
         <v>3.8</v>
       </c>
-      <c r="H13" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="I13" t="n">
-        <v>2.78</v>
-      </c>
-      <c r="J13" t="n">
-        <v>3.25</v>
-      </c>
       <c r="K13" t="n">
-        <v>7.4</v>
+        <v>4.8</v>
       </c>
       <c r="L13" t="n">
         <v>0</v>
@@ -3681,10 +3681,10 @@
         <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>1.95</v>
+        <v>2.44</v>
       </c>
       <c r="Q13" t="n">
-        <v>1.65</v>
+        <v>1.58</v>
       </c>
       <c r="R13" t="n">
         <v>0</v>
@@ -3874,14 +3874,14 @@
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-05-14 00:34:16</t>
+          <t>2026-05-14 02:53:36</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Chinese Super League</t>
+          <t>Indonesian Super League</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -3896,31 +3896,31 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Yunnan Yukun</t>
+          <t>Persis Solo</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Shanghai Shenhua</t>
+          <t>Dewa United FC</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>2.08</v>
+        <v>2.72</v>
       </c>
       <c r="G14" t="n">
-        <v>2.26</v>
+        <v>3.8</v>
       </c>
       <c r="H14" t="n">
-        <v>3.1</v>
+        <v>2.06</v>
       </c>
       <c r="I14" t="n">
-        <v>3.35</v>
+        <v>2.82</v>
       </c>
       <c r="J14" t="n">
-        <v>4.2</v>
+        <v>3.5</v>
       </c>
       <c r="K14" t="n">
-        <v>5.1</v>
+        <v>7</v>
       </c>
       <c r="L14" t="n">
         <v>0</v>
@@ -3935,10 +3935,10 @@
         <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>3.3</v>
+        <v>1.95</v>
       </c>
       <c r="Q14" t="n">
-        <v>1.32</v>
+        <v>1.65</v>
       </c>
       <c r="R14" t="n">
         <v>0</v>
@@ -4128,14 +4128,14 @@
       </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>2026-05-14 00:34:16</t>
+          <t>2026-05-14 02:53:36</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Indonesian Super League</t>
+          <t>Spanish Segunda Division</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -4150,239 +4150,239 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Malut United</t>
+          <t>Sociedad B</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Persita Tangerang</t>
+          <t>Mirandes</t>
         </is>
       </c>
       <c r="F15" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="G15" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="H15" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="I15" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="J15" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="K15" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="L15" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="M15" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="N15" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="O15" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="P15" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="Q15" t="n">
         <v>1.68</v>
       </c>
-      <c r="G15" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="H15" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="I15" t="n">
+      <c r="R15" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="S15" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="T15" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="U15" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="V15" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="W15" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="X15" t="n">
+        <v>23</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>12</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>32</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>17</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>23</v>
+      </c>
+      <c r="AF15" t="n">
+        <v>28</v>
+      </c>
+      <c r="AG15" t="n">
+        <v>16</v>
+      </c>
+      <c r="AH15" t="n">
+        <v>21</v>
+      </c>
+      <c r="AI15" t="n">
+        <v>32</v>
+      </c>
+      <c r="AJ15" t="n">
+        <v>65</v>
+      </c>
+      <c r="AK15" t="n">
+        <v>40</v>
+      </c>
+      <c r="AL15" t="n">
+        <v>46</v>
+      </c>
+      <c r="AM15" t="n">
+        <v>95</v>
+      </c>
+      <c r="AN15" t="n">
+        <v>34</v>
+      </c>
+      <c r="AO15" t="n">
+        <v>15</v>
+      </c>
+      <c r="AP15" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="AQ15" t="n">
+        <v>10</v>
+      </c>
+      <c r="AR15" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AS15" t="n">
+        <v>20</v>
+      </c>
+      <c r="AT15" t="n">
+        <v>13</v>
+      </c>
+      <c r="AU15" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AV15" t="n">
+        <v>8</v>
+      </c>
+      <c r="AW15" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="AX15" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="AY15" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AZ15" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="BA15" t="n">
         <v>5.7</v>
       </c>
-      <c r="J15" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="K15" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="L15" t="n">
-        <v>0</v>
-      </c>
-      <c r="M15" t="n">
-        <v>0</v>
-      </c>
-      <c r="N15" t="n">
-        <v>0</v>
-      </c>
-      <c r="O15" t="n">
-        <v>0</v>
-      </c>
-      <c r="P15" t="n">
-        <v>2.44</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="R15" t="n">
-        <v>0</v>
-      </c>
-      <c r="S15" t="n">
-        <v>0</v>
-      </c>
-      <c r="T15" t="n">
-        <v>0</v>
-      </c>
-      <c r="U15" t="n">
-        <v>0</v>
-      </c>
-      <c r="V15" t="n">
-        <v>0</v>
-      </c>
-      <c r="W15" t="n">
-        <v>0</v>
-      </c>
-      <c r="X15" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y15" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ15" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA15" t="n">
-        <v>0</v>
-      </c>
       <c r="BB15" t="n">
-        <v>0</v>
+        <v>6.2</v>
       </c>
       <c r="BC15" t="n">
-        <v>0</v>
+        <v>5.9</v>
       </c>
       <c r="BD15" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="BE15" t="n">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="BF15" t="n">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="BG15" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="BH15" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="BI15" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="BJ15" t="n">
-        <v>0</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BK15" t="n">
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="BL15" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM15" t="n">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="BN15" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="BO15" t="n">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="BP15" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ15" t="n">
-        <v>0</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BR15" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS15" t="n">
-        <v>0</v>
+        <v>9.6</v>
       </c>
       <c r="BT15" t="n">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="BU15" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="BV15" t="n">
-        <v>0</v>
+        <v>15.5</v>
       </c>
       <c r="BW15" t="n">
-        <v>0</v>
+        <v>7.2</v>
       </c>
       <c r="BX15" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY15" t="n">
-        <v>0</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BZ15" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="CA15" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="CB15" t="inlineStr">
         <is>
-          <t>2026-05-14 00:34:16</t>
+          <t>2026-05-14 02:53:36</t>
         </is>
       </c>
     </row>
@@ -4416,7 +4416,7 @@
         <v>2.88</v>
       </c>
       <c r="G16" t="n">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="H16" t="n">
         <v>2.36</v>
@@ -4425,7 +4425,7 @@
         <v>2.66</v>
       </c>
       <c r="J16" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="K16" t="n">
         <v>4.1</v>
@@ -4443,10 +4443,10 @@
         <v>0</v>
       </c>
       <c r="P16" t="n">
-        <v>1.96</v>
+        <v>1.99</v>
       </c>
       <c r="Q16" t="n">
-        <v>1.86</v>
+        <v>1.71</v>
       </c>
       <c r="R16" t="n">
         <v>0</v>
@@ -4636,14 +4636,14 @@
       </c>
       <c r="CB16" t="inlineStr">
         <is>
-          <t>2026-05-14 00:34:16</t>
+          <t>2026-05-14 02:53:36</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Azerbaijan Premier League</t>
+          <t>Latvian Virsliga</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -4658,31 +4658,31 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Qarabag FK</t>
+          <t>SK Super Nova</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Imisli FK</t>
+          <t>Ogre United</t>
         </is>
       </c>
       <c r="F17" t="n">
         <v>1.04</v>
       </c>
       <c r="G17" t="n">
-        <v>600</v>
+        <v>640</v>
       </c>
       <c r="H17" t="n">
         <v>1.04</v>
       </c>
       <c r="I17" t="n">
-        <v>870</v>
+        <v>750</v>
       </c>
       <c r="J17" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="K17" t="n">
-        <v>500</v>
+        <v>370</v>
       </c>
       <c r="L17" t="n">
         <v>0</v>
@@ -4890,14 +4890,14 @@
       </c>
       <c r="CB17" t="inlineStr">
         <is>
-          <t>2026-05-14 00:34:16</t>
+          <t>2026-05-14 02:53:36</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Azerbaijan Premier League</t>
+          <t>Bulgarian A League</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -4912,31 +4912,31 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Shamakhi FK</t>
+          <t>CSKA 1948 Sofia</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>PFK Turan Tovuz</t>
+          <t>Ludogorets</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>1.04</v>
+        <v>3.4</v>
       </c>
       <c r="G18" t="n">
-        <v>1000</v>
+        <v>4.4</v>
       </c>
       <c r="H18" t="n">
-        <v>1.04</v>
+        <v>2.14</v>
       </c>
       <c r="I18" t="n">
-        <v>1000</v>
+        <v>2.5</v>
       </c>
       <c r="J18" t="n">
-        <v>1.01</v>
+        <v>2.68</v>
       </c>
       <c r="K18" t="n">
-        <v>1000</v>
+        <v>4.2</v>
       </c>
       <c r="L18" t="n">
         <v>0</v>
@@ -4951,10 +4951,10 @@
         <v>0</v>
       </c>
       <c r="P18" t="n">
-        <v>1.24</v>
+        <v>1.8</v>
       </c>
       <c r="Q18" t="n">
-        <v>1.01</v>
+        <v>1.98</v>
       </c>
       <c r="R18" t="n">
         <v>0</v>
@@ -5144,7 +5144,7 @@
       </c>
       <c r="CB18" t="inlineStr">
         <is>
-          <t>2026-05-14 00:34:16</t>
+          <t>2026-05-14 02:53:36</t>
         </is>
       </c>
     </row>
@@ -5166,31 +5166,31 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>CSKA 1948 Sofia</t>
+          <t>PFC Levski Sofia</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Ludogorets</t>
+          <t>CSKA Sofia</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>3.4</v>
+        <v>2.12</v>
       </c>
       <c r="G19" t="n">
-        <v>4.4</v>
+        <v>2.94</v>
       </c>
       <c r="H19" t="n">
-        <v>2.14</v>
+        <v>2.8</v>
       </c>
       <c r="I19" t="n">
-        <v>2.5</v>
+        <v>4.3</v>
       </c>
       <c r="J19" t="n">
-        <v>2.68</v>
+        <v>2.34</v>
       </c>
       <c r="K19" t="n">
-        <v>4.2</v>
+        <v>5.9</v>
       </c>
       <c r="L19" t="n">
         <v>0</v>
@@ -5205,10 +5205,10 @@
         <v>0</v>
       </c>
       <c r="P19" t="n">
-        <v>1.8</v>
+        <v>1.45</v>
       </c>
       <c r="Q19" t="n">
-        <v>1.98</v>
+        <v>2.24</v>
       </c>
       <c r="R19" t="n">
         <v>0</v>
@@ -5398,14 +5398,14 @@
       </c>
       <c r="CB19" t="inlineStr">
         <is>
-          <t>2026-05-14 00:34:16</t>
+          <t>2026-05-14 02:53:36</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Bulgarian A League</t>
+          <t>Azerbaijan Premier League</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -5420,31 +5420,31 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>PFC Levski Sofia</t>
+          <t>Qarabag FK</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>CSKA Sofia</t>
+          <t>Imisli FK</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>2.16</v>
+        <v>1.04</v>
       </c>
       <c r="G20" t="n">
-        <v>2.82</v>
+        <v>600</v>
       </c>
       <c r="H20" t="n">
-        <v>2.8</v>
+        <v>1.04</v>
       </c>
       <c r="I20" t="n">
-        <v>4.1</v>
+        <v>870</v>
       </c>
       <c r="J20" t="n">
-        <v>2.48</v>
+        <v>1.02</v>
       </c>
       <c r="K20" t="n">
-        <v>5.6</v>
+        <v>500</v>
       </c>
       <c r="L20" t="n">
         <v>0</v>
@@ -5459,10 +5459,10 @@
         <v>0</v>
       </c>
       <c r="P20" t="n">
-        <v>1.45</v>
+        <v>1.24</v>
       </c>
       <c r="Q20" t="n">
-        <v>2.24</v>
+        <v>1.01</v>
       </c>
       <c r="R20" t="n">
         <v>0</v>
@@ -5652,14 +5652,14 @@
       </c>
       <c r="CB20" t="inlineStr">
         <is>
-          <t>2026-05-14 00:34:16</t>
+          <t>2026-05-14 02:53:36</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Latvian Virsliga</t>
+          <t>Azerbaijan Premier League</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -5674,31 +5674,31 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>SK Super Nova</t>
+          <t>Shamakhi FK</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Ogre United</t>
+          <t>PFK Turan Tovuz</t>
         </is>
       </c>
       <c r="F21" t="n">
         <v>1.04</v>
       </c>
       <c r="G21" t="n">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="H21" t="n">
         <v>1.04</v>
       </c>
       <c r="I21" t="n">
-        <v>1000</v>
+        <v>870</v>
       </c>
       <c r="J21" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="K21" t="n">
-        <v>370</v>
+        <v>710</v>
       </c>
       <c r="L21" t="n">
         <v>0</v>
@@ -5906,7 +5906,7 @@
       </c>
       <c r="CB21" t="inlineStr">
         <is>
-          <t>2026-05-14 00:34:16</t>
+          <t>2026-05-14 02:53:36</t>
         </is>
       </c>
     </row>
@@ -5937,22 +5937,22 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="G22" t="n">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="H22" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="I22" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="J22" t="n">
         <v>5.3</v>
       </c>
       <c r="K22" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="L22" t="n">
         <v>0</v>
@@ -6160,7 +6160,7 @@
       </c>
       <c r="CB22" t="inlineStr">
         <is>
-          <t>2026-05-14 00:34:16</t>
+          <t>2026-05-14 02:53:36</t>
         </is>
       </c>
     </row>
@@ -6221,10 +6221,10 @@
         <v>0</v>
       </c>
       <c r="P23" t="n">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="Q23" t="n">
-        <v>1.83</v>
+        <v>1.92</v>
       </c>
       <c r="R23" t="n">
         <v>0</v>
@@ -6414,7 +6414,7 @@
       </c>
       <c r="CB23" t="inlineStr">
         <is>
-          <t>2026-05-14 00:34:16</t>
+          <t>2026-05-14 02:53:36</t>
         </is>
       </c>
     </row>
@@ -6668,7 +6668,7 @@
       </c>
       <c r="CB24" t="inlineStr">
         <is>
-          <t>2026-05-14 00:34:16</t>
+          <t>2026-05-14 02:53:36</t>
         </is>
       </c>
     </row>
@@ -6702,10 +6702,10 @@
         <v>1.58</v>
       </c>
       <c r="G25" t="n">
-        <v>1.83</v>
+        <v>1.71</v>
       </c>
       <c r="H25" t="n">
-        <v>3.5</v>
+        <v>5.1</v>
       </c>
       <c r="I25" t="n">
         <v>7</v>
@@ -6732,7 +6732,7 @@
         <v>2.52</v>
       </c>
       <c r="Q25" t="n">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="R25" t="n">
         <v>0</v>
@@ -6922,7 +6922,7 @@
       </c>
       <c r="CB25" t="inlineStr">
         <is>
-          <t>2026-05-14 00:34:16</t>
+          <t>2026-05-14 02:53:36</t>
         </is>
       </c>
     </row>
@@ -7176,7 +7176,7 @@
       </c>
       <c r="CB26" t="inlineStr">
         <is>
-          <t>2026-05-14 00:34:16</t>
+          <t>2026-05-14 02:53:36</t>
         </is>
       </c>
     </row>
@@ -7430,14 +7430,14 @@
       </c>
       <c r="CB27" t="inlineStr">
         <is>
-          <t>2026-05-14 00:34:16</t>
+          <t>2026-05-14 02:53:36</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Belgian Pro League</t>
+          <t>Norwegian 1st Division</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -7452,31 +7452,31 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Charleroi</t>
+          <t>Hodd</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Westerlo</t>
+          <t>Sogndal</t>
         </is>
       </c>
       <c r="F28" t="n">
-        <v>2.04</v>
+        <v>2.66</v>
       </c>
       <c r="G28" t="n">
-        <v>2.24</v>
+        <v>2.94</v>
       </c>
       <c r="H28" t="n">
-        <v>3.35</v>
+        <v>2.5</v>
       </c>
       <c r="I28" t="n">
-        <v>4</v>
+        <v>2.74</v>
       </c>
       <c r="J28" t="n">
-        <v>3.85</v>
+        <v>3.65</v>
       </c>
       <c r="K28" t="n">
-        <v>4.5</v>
+        <v>4.1</v>
       </c>
       <c r="L28" t="n">
         <v>0</v>
@@ -7491,10 +7491,10 @@
         <v>0</v>
       </c>
       <c r="P28" t="n">
-        <v>2.34</v>
+        <v>2.02</v>
       </c>
       <c r="Q28" t="n">
-        <v>1.61</v>
+        <v>1.57</v>
       </c>
       <c r="R28" t="n">
         <v>0</v>
@@ -7684,14 +7684,14 @@
       </c>
       <c r="CB28" t="inlineStr">
         <is>
-          <t>2026-05-14 00:34:16</t>
+          <t>2026-05-14 02:53:36</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Norwegian 1st Division</t>
+          <t>Lithuanian A Lyga</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -7706,31 +7706,31 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Hodd</t>
+          <t>Hegelmann Litauen</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Sogndal</t>
+          <t>FK Suduva</t>
         </is>
       </c>
       <c r="F29" t="n">
-        <v>2.66</v>
+        <v>1.04</v>
       </c>
       <c r="G29" t="n">
-        <v>2.94</v>
+        <v>600</v>
       </c>
       <c r="H29" t="n">
-        <v>2.5</v>
+        <v>2.2</v>
       </c>
       <c r="I29" t="n">
-        <v>2.74</v>
+        <v>870</v>
       </c>
       <c r="J29" t="n">
-        <v>3.65</v>
+        <v>1.02</v>
       </c>
       <c r="K29" t="n">
-        <v>4.1</v>
+        <v>540</v>
       </c>
       <c r="L29" t="n">
         <v>0</v>
@@ -7745,10 +7745,10 @@
         <v>0</v>
       </c>
       <c r="P29" t="n">
-        <v>2.24</v>
+        <v>1.24</v>
       </c>
       <c r="Q29" t="n">
-        <v>1.57</v>
+        <v>1.01</v>
       </c>
       <c r="R29" t="n">
         <v>0</v>
@@ -7938,14 +7938,14 @@
       </c>
       <c r="CB29" t="inlineStr">
         <is>
-          <t>2026-05-14 00:34:16</t>
+          <t>2026-05-14 02:53:36</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Lithuanian A Lyga</t>
+          <t>Estonian Premier League</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -7960,12 +7960,12 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Hegelmann Litauen</t>
+          <t>Harju JK Laagri</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>FK Suduva</t>
+          <t>Parnu JK Vaprus</t>
         </is>
       </c>
       <c r="F30" t="n">
@@ -7975,16 +7975,16 @@
         <v>600</v>
       </c>
       <c r="H30" t="n">
-        <v>2.2</v>
+        <v>1.04</v>
       </c>
       <c r="I30" t="n">
         <v>870</v>
       </c>
       <c r="J30" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="K30" t="n">
-        <v>540</v>
+        <v>500</v>
       </c>
       <c r="L30" t="n">
         <v>0</v>
@@ -8192,14 +8192,14 @@
       </c>
       <c r="CB30" t="inlineStr">
         <is>
-          <t>2026-05-14 00:34:16</t>
+          <t>2026-05-14 02:53:36</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Estonian Premier League</t>
+          <t>Croatian HNL</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -8214,31 +8214,31 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Harju JK Laagri</t>
+          <t>HNK Gorica</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Parnu JK Vaprus</t>
+          <t>Osijek</t>
         </is>
       </c>
       <c r="F31" t="n">
-        <v>1.04</v>
+        <v>2.2</v>
       </c>
       <c r="G31" t="n">
-        <v>600</v>
+        <v>2.5</v>
       </c>
       <c r="H31" t="n">
-        <v>1.04</v>
+        <v>3.3</v>
       </c>
       <c r="I31" t="n">
-        <v>870</v>
+        <v>4.3</v>
       </c>
       <c r="J31" t="n">
-        <v>1.01</v>
+        <v>3.1</v>
       </c>
       <c r="K31" t="n">
-        <v>500</v>
+        <v>3.65</v>
       </c>
       <c r="L31" t="n">
         <v>0</v>
@@ -8253,10 +8253,10 @@
         <v>0</v>
       </c>
       <c r="P31" t="n">
-        <v>1.24</v>
+        <v>1.71</v>
       </c>
       <c r="Q31" t="n">
-        <v>1.01</v>
+        <v>2.12</v>
       </c>
       <c r="R31" t="n">
         <v>0</v>
@@ -8446,14 +8446,14 @@
       </c>
       <c r="CB31" t="inlineStr">
         <is>
-          <t>2026-05-14 00:34:16</t>
+          <t>2026-05-14 02:53:36</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Croatian HNL</t>
+          <t>Belgian Pro League</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -8468,31 +8468,31 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>HNK Gorica</t>
+          <t>Charleroi</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Osijek</t>
+          <t>Westerlo</t>
         </is>
       </c>
       <c r="F32" t="n">
-        <v>2.2</v>
+        <v>2.04</v>
       </c>
       <c r="G32" t="n">
-        <v>2.5</v>
+        <v>2.24</v>
       </c>
       <c r="H32" t="n">
         <v>3.35</v>
       </c>
       <c r="I32" t="n">
-        <v>4.2</v>
+        <v>3.7</v>
       </c>
       <c r="J32" t="n">
-        <v>3.1</v>
+        <v>3.85</v>
       </c>
       <c r="K32" t="n">
-        <v>3.65</v>
+        <v>4.5</v>
       </c>
       <c r="L32" t="n">
         <v>0</v>
@@ -8507,10 +8507,10 @@
         <v>0</v>
       </c>
       <c r="P32" t="n">
-        <v>1.71</v>
+        <v>2.34</v>
       </c>
       <c r="Q32" t="n">
-        <v>2.12</v>
+        <v>1.61</v>
       </c>
       <c r="R32" t="n">
         <v>0</v>
@@ -8700,7 +8700,7 @@
       </c>
       <c r="CB32" t="inlineStr">
         <is>
-          <t>2026-05-14 00:34:16</t>
+          <t>2026-05-14 02:53:36</t>
         </is>
       </c>
     </row>
@@ -8740,10 +8740,10 @@
         <v>1.97</v>
       </c>
       <c r="I33" t="n">
-        <v>2.18</v>
+        <v>2.28</v>
       </c>
       <c r="J33" t="n">
-        <v>3.65</v>
+        <v>3.9</v>
       </c>
       <c r="K33" t="n">
         <v>5</v>
@@ -8954,7 +8954,7 @@
       </c>
       <c r="CB33" t="inlineStr">
         <is>
-          <t>2026-05-14 00:34:16</t>
+          <t>2026-05-14 02:53:36</t>
         </is>
       </c>
     </row>
@@ -8976,31 +8976,31 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>AD Ceuta FC</t>
+          <t>Leonesa</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Malaga</t>
+          <t>Eibar</t>
         </is>
       </c>
       <c r="F34" t="n">
-        <v>4.6</v>
+        <v>3.2</v>
       </c>
       <c r="G34" t="n">
-        <v>5.5</v>
+        <v>3.45</v>
       </c>
       <c r="H34" t="n">
-        <v>1.73</v>
+        <v>2.38</v>
       </c>
       <c r="I34" t="n">
-        <v>1.85</v>
+        <v>2.54</v>
       </c>
       <c r="J34" t="n">
-        <v>4</v>
+        <v>3.25</v>
       </c>
       <c r="K34" t="n">
-        <v>4.5</v>
+        <v>3.55</v>
       </c>
       <c r="L34" t="n">
         <v>0</v>
@@ -9015,11 +9015,11 @@
         <v>0</v>
       </c>
       <c r="P34" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="Q34" t="n">
         <v>2.1</v>
       </c>
-      <c r="Q34" t="n">
-        <v>1.65</v>
-      </c>
       <c r="R34" t="n">
         <v>0</v>
       </c>
@@ -9208,7 +9208,7 @@
       </c>
       <c r="CB34" t="inlineStr">
         <is>
-          <t>2026-05-14 00:34:16</t>
+          <t>2026-05-14 02:53:36</t>
         </is>
       </c>
     </row>
@@ -9230,31 +9230,31 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Leonesa</t>
+          <t>AD Ceuta FC</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Eibar</t>
+          <t>Malaga</t>
         </is>
       </c>
       <c r="F35" t="n">
-        <v>3.2</v>
+        <v>4.6</v>
       </c>
       <c r="G35" t="n">
-        <v>3.45</v>
+        <v>5.5</v>
       </c>
       <c r="H35" t="n">
-        <v>2.36</v>
+        <v>1.73</v>
       </c>
       <c r="I35" t="n">
-        <v>2.54</v>
+        <v>1.85</v>
       </c>
       <c r="J35" t="n">
-        <v>3.25</v>
+        <v>4</v>
       </c>
       <c r="K35" t="n">
-        <v>3.6</v>
+        <v>4.4</v>
       </c>
       <c r="L35" t="n">
         <v>0</v>
@@ -9269,10 +9269,10 @@
         <v>0</v>
       </c>
       <c r="P35" t="n">
-        <v>1.79</v>
+        <v>2.1</v>
       </c>
       <c r="Q35" t="n">
-        <v>2.1</v>
+        <v>1.65</v>
       </c>
       <c r="R35" t="n">
         <v>0</v>
@@ -9462,14 +9462,14 @@
       </c>
       <c r="CB35" t="inlineStr">
         <is>
-          <t>2026-05-14 00:34:16</t>
+          <t>2026-05-14 02:53:36</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Israeli Premier League</t>
+          <t>Swedish Superettan</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -9484,31 +9484,31 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Maccabi Haifa</t>
+          <t>IK Brage</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Hapoel Petach Tikva</t>
+          <t>Norrkoping</t>
         </is>
       </c>
       <c r="F36" t="n">
-        <v>1.48</v>
+        <v>2.72</v>
       </c>
       <c r="G36" t="n">
-        <v>1.85</v>
+        <v>3.25</v>
       </c>
       <c r="H36" t="n">
-        <v>2.22</v>
+        <v>2.38</v>
       </c>
       <c r="I36" t="n">
-        <v>870</v>
+        <v>2.76</v>
       </c>
       <c r="J36" t="n">
-        <v>3.9</v>
+        <v>3.55</v>
       </c>
       <c r="K36" t="n">
-        <v>500</v>
+        <v>4.8</v>
       </c>
       <c r="L36" t="n">
         <v>0</v>
@@ -9523,10 +9523,10 @@
         <v>0</v>
       </c>
       <c r="P36" t="n">
-        <v>1.24</v>
+        <v>2.28</v>
       </c>
       <c r="Q36" t="n">
-        <v>1.38</v>
+        <v>1.58</v>
       </c>
       <c r="R36" t="n">
         <v>0</v>
@@ -9716,14 +9716,14 @@
       </c>
       <c r="CB36" t="inlineStr">
         <is>
-          <t>2026-05-14 00:34:16</t>
+          <t>2026-05-14 02:53:36</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Swedish Superettan</t>
+          <t>Uruguayan Primera Division</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -9738,31 +9738,31 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>IK Brage</t>
+          <t>Boston River</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Norrkoping</t>
+          <t>Cerro</t>
         </is>
       </c>
       <c r="F37" t="n">
-        <v>2.72</v>
+        <v>2.08</v>
       </c>
       <c r="G37" t="n">
-        <v>3.25</v>
+        <v>2.4</v>
       </c>
       <c r="H37" t="n">
-        <v>2.38</v>
+        <v>3.85</v>
       </c>
       <c r="I37" t="n">
-        <v>2.76</v>
+        <v>5.1</v>
       </c>
       <c r="J37" t="n">
-        <v>3.55</v>
+        <v>3.1</v>
       </c>
       <c r="K37" t="n">
-        <v>4.8</v>
+        <v>3.9</v>
       </c>
       <c r="L37" t="n">
         <v>0</v>
@@ -9777,10 +9777,10 @@
         <v>0</v>
       </c>
       <c r="P37" t="n">
-        <v>2.28</v>
+        <v>1.56</v>
       </c>
       <c r="Q37" t="n">
-        <v>1.58</v>
+        <v>2.42</v>
       </c>
       <c r="R37" t="n">
         <v>0</v>
@@ -9970,14 +9970,14 @@
       </c>
       <c r="CB37" t="inlineStr">
         <is>
-          <t>2026-05-14 00:34:16</t>
+          <t>2026-05-14 02:53:36</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Uruguayan Primera Division</t>
+          <t>Israeli Premier League</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -9992,31 +9992,31 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Boston River</t>
+          <t>Maccabi Haifa</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Cerro</t>
+          <t>Hapoel Petach Tikva</t>
         </is>
       </c>
       <c r="F38" t="n">
-        <v>2.08</v>
+        <v>1.48</v>
       </c>
       <c r="G38" t="n">
-        <v>2.36</v>
+        <v>1.85</v>
       </c>
       <c r="H38" t="n">
-        <v>3.85</v>
+        <v>2.22</v>
       </c>
       <c r="I38" t="n">
-        <v>5.1</v>
+        <v>870</v>
       </c>
       <c r="J38" t="n">
-        <v>3</v>
+        <v>3.9</v>
       </c>
       <c r="K38" t="n">
-        <v>3.9</v>
+        <v>500</v>
       </c>
       <c r="L38" t="n">
         <v>0</v>
@@ -10031,10 +10031,10 @@
         <v>0</v>
       </c>
       <c r="P38" t="n">
-        <v>1.56</v>
+        <v>1.24</v>
       </c>
       <c r="Q38" t="n">
-        <v>2.42</v>
+        <v>1.38</v>
       </c>
       <c r="R38" t="n">
         <v>0</v>
@@ -10224,7 +10224,7 @@
       </c>
       <c r="CB38" t="inlineStr">
         <is>
-          <t>2026-05-14 00:34:16</t>
+          <t>2026-05-14 02:53:36</t>
         </is>
       </c>
     </row>
@@ -10258,7 +10258,7 @@
         <v>1.17</v>
       </c>
       <c r="G39" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="H39" t="n">
         <v>1.33</v>
@@ -10285,10 +10285,10 @@
         <v>0</v>
       </c>
       <c r="P39" t="n">
-        <v>2.26</v>
+        <v>2.36</v>
       </c>
       <c r="Q39" t="n">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="R39" t="n">
         <v>0</v>
@@ -10478,7 +10478,7 @@
       </c>
       <c r="CB39" t="inlineStr">
         <is>
-          <t>2026-05-14 00:34:16</t>
+          <t>2026-05-14 02:53:36</t>
         </is>
       </c>
     </row>
@@ -10500,31 +10500,31 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Diosgyori</t>
+          <t>Ferencvaros</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Paks</t>
+          <t>Zalaegerszeg</t>
         </is>
       </c>
       <c r="F40" t="n">
-        <v>2.44</v>
+        <v>1.26</v>
       </c>
       <c r="G40" t="n">
-        <v>600</v>
+        <v>1.49</v>
       </c>
       <c r="H40" t="n">
-        <v>1.39</v>
+        <v>7</v>
       </c>
       <c r="I40" t="n">
-        <v>1.7</v>
+        <v>660</v>
       </c>
       <c r="J40" t="n">
-        <v>2.42</v>
+        <v>4.7</v>
       </c>
       <c r="K40" t="n">
-        <v>500</v>
+        <v>16</v>
       </c>
       <c r="L40" t="n">
         <v>0</v>
@@ -10539,10 +10539,10 @@
         <v>0</v>
       </c>
       <c r="P40" t="n">
-        <v>2.96</v>
+        <v>2.26</v>
       </c>
       <c r="Q40" t="n">
-        <v>1.25</v>
+        <v>1.44</v>
       </c>
       <c r="R40" t="n">
         <v>0</v>
@@ -10732,7 +10732,7 @@
       </c>
       <c r="CB40" t="inlineStr">
         <is>
-          <t>2026-05-14 00:34:16</t>
+          <t>2026-05-14 02:53:36</t>
         </is>
       </c>
     </row>
@@ -10793,10 +10793,10 @@
         <v>0</v>
       </c>
       <c r="P41" t="n">
-        <v>1.25</v>
+        <v>2.1</v>
       </c>
       <c r="Q41" t="n">
-        <v>1.52</v>
+        <v>1.6</v>
       </c>
       <c r="R41" t="n">
         <v>0</v>
@@ -10986,7 +10986,7 @@
       </c>
       <c r="CB41" t="inlineStr">
         <is>
-          <t>2026-05-14 00:34:16</t>
+          <t>2026-05-14 02:53:36</t>
         </is>
       </c>
     </row>
@@ -11008,31 +11008,31 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Ferencvaros</t>
+          <t>Diosgyori</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Zalaegerszeg</t>
+          <t>Paks</t>
         </is>
       </c>
       <c r="F42" t="n">
-        <v>1.26</v>
+        <v>4.7</v>
       </c>
       <c r="G42" t="n">
-        <v>1.49</v>
+        <v>600</v>
       </c>
       <c r="H42" t="n">
-        <v>3.1</v>
+        <v>1.39</v>
       </c>
       <c r="I42" t="n">
-        <v>1000</v>
+        <v>1.7</v>
       </c>
       <c r="J42" t="n">
-        <v>4.7</v>
+        <v>4.3</v>
       </c>
       <c r="K42" t="n">
-        <v>460</v>
+        <v>500</v>
       </c>
       <c r="L42" t="n">
         <v>0</v>
@@ -11047,10 +11047,10 @@
         <v>0</v>
       </c>
       <c r="P42" t="n">
-        <v>2.26</v>
+        <v>2.96</v>
       </c>
       <c r="Q42" t="n">
-        <v>1.44</v>
+        <v>1.25</v>
       </c>
       <c r="R42" t="n">
         <v>0</v>
@@ -11240,14 +11240,14 @@
       </c>
       <c r="CB42" t="inlineStr">
         <is>
-          <t>2026-05-14 00:34:16</t>
+          <t>2026-05-14 02:53:36</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Romanian Liga I</t>
+          <t>Lithuanian A Lyga</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -11262,31 +11262,31 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Csikszereda</t>
+          <t>FC Dziugas</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Botosani</t>
+          <t>FK Banga Gargzdu</t>
         </is>
       </c>
       <c r="F43" t="n">
-        <v>2.74</v>
+        <v>1.04</v>
       </c>
       <c r="G43" t="n">
-        <v>3.3</v>
+        <v>470</v>
       </c>
       <c r="H43" t="n">
-        <v>2.6</v>
+        <v>1.04</v>
       </c>
       <c r="I43" t="n">
-        <v>3.1</v>
+        <v>590</v>
       </c>
       <c r="J43" t="n">
-        <v>2.66</v>
+        <v>1.02</v>
       </c>
       <c r="K43" t="n">
-        <v>3.7</v>
+        <v>710</v>
       </c>
       <c r="L43" t="n">
         <v>0</v>
@@ -11301,10 +11301,10 @@
         <v>0</v>
       </c>
       <c r="P43" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="Q43" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="R43" t="n">
         <v>0</v>
@@ -11494,7 +11494,7 @@
       </c>
       <c r="CB43" t="inlineStr">
         <is>
-          <t>2026-05-14 00:34:16</t>
+          <t>2026-05-14 02:53:36</t>
         </is>
       </c>
     </row>
@@ -11748,14 +11748,14 @@
       </c>
       <c r="CB44" t="inlineStr">
         <is>
-          <t>2026-05-14 00:34:16</t>
+          <t>2026-05-14 02:53:36</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Lithuanian A Lyga</t>
+          <t>Romanian Liga I</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -11770,31 +11770,31 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>FC Dziugas</t>
+          <t>Csikszereda</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>FK Banga Gargzdu</t>
+          <t>Botosani</t>
         </is>
       </c>
       <c r="F45" t="n">
-        <v>1.04</v>
+        <v>2.74</v>
       </c>
       <c r="G45" t="n">
-        <v>1000</v>
+        <v>3.25</v>
       </c>
       <c r="H45" t="n">
-        <v>1.04</v>
+        <v>2.6</v>
       </c>
       <c r="I45" t="n">
-        <v>1000</v>
+        <v>3.05</v>
       </c>
       <c r="J45" t="n">
-        <v>1.01</v>
+        <v>3.3</v>
       </c>
       <c r="K45" t="n">
-        <v>710</v>
+        <v>3.7</v>
       </c>
       <c r="L45" t="n">
         <v>0</v>
@@ -11809,10 +11809,10 @@
         <v>0</v>
       </c>
       <c r="P45" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="Q45" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="R45" t="n">
         <v>0</v>
@@ -12002,14 +12002,14 @@
       </c>
       <c r="CB45" t="inlineStr">
         <is>
-          <t>2026-05-14 00:34:16</t>
+          <t>2026-05-14 02:53:36</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Bulgarian A League</t>
+          <t>Swiss Super League</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -12024,31 +12024,31 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Arda</t>
+          <t>Lausanne</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Lokomotiv Plovdiv</t>
+          <t>Grasshoppers Zurich</t>
         </is>
       </c>
       <c r="F46" t="n">
-        <v>1.76</v>
+        <v>1.58</v>
       </c>
       <c r="G46" t="n">
-        <v>1.85</v>
+        <v>1.64</v>
       </c>
       <c r="H46" t="n">
-        <v>5.2</v>
+        <v>5.4</v>
       </c>
       <c r="I46" t="n">
-        <v>5.9</v>
+        <v>6.4</v>
       </c>
       <c r="J46" t="n">
-        <v>3.6</v>
+        <v>4.3</v>
       </c>
       <c r="K46" t="n">
-        <v>4.1</v>
+        <v>5.1</v>
       </c>
       <c r="L46" t="n">
         <v>0</v>
@@ -12063,10 +12063,10 @@
         <v>0</v>
       </c>
       <c r="P46" t="n">
-        <v>1.73</v>
+        <v>2.62</v>
       </c>
       <c r="Q46" t="n">
-        <v>1.93</v>
+        <v>1.44</v>
       </c>
       <c r="R46" t="n">
         <v>0</v>
@@ -12256,14 +12256,14 @@
       </c>
       <c r="CB46" t="inlineStr">
         <is>
-          <t>2026-05-14 00:34:16</t>
+          <t>2026-05-14 02:53:36</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Bulgarian A League</t>
+          <t>Swiss Super League</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -12278,31 +12278,31 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Botev Plovdiv</t>
+          <t>Winterthur</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Cherno More</t>
+          <t>Luzern</t>
         </is>
       </c>
       <c r="F47" t="n">
-        <v>2.36</v>
+        <v>3.85</v>
       </c>
       <c r="G47" t="n">
-        <v>3.4</v>
+        <v>4.3</v>
       </c>
       <c r="H47" t="n">
-        <v>2.58</v>
+        <v>1.9</v>
       </c>
       <c r="I47" t="n">
-        <v>3.8</v>
+        <v>2.04</v>
       </c>
       <c r="J47" t="n">
-        <v>2.76</v>
+        <v>4</v>
       </c>
       <c r="K47" t="n">
-        <v>5.4</v>
+        <v>4.7</v>
       </c>
       <c r="L47" t="n">
         <v>0</v>
@@ -12317,10 +12317,10 @@
         <v>0</v>
       </c>
       <c r="P47" t="n">
-        <v>1.52</v>
+        <v>3.2</v>
       </c>
       <c r="Q47" t="n">
-        <v>2.08</v>
+        <v>1.35</v>
       </c>
       <c r="R47" t="n">
         <v>0</v>
@@ -12510,14 +12510,14 @@
       </c>
       <c r="CB47" t="inlineStr">
         <is>
-          <t>2026-05-14 00:34:16</t>
+          <t>2026-05-14 02:53:36</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Latvian Virsliga</t>
+          <t>Swiss Super League</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -12532,31 +12532,31 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>FK Riga</t>
+          <t>FC Zurich</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>FK Jelgava</t>
+          <t>Servette</t>
         </is>
       </c>
       <c r="F48" t="n">
-        <v>1.04</v>
+        <v>3.15</v>
       </c>
       <c r="G48" t="n">
-        <v>1000</v>
+        <v>3.95</v>
       </c>
       <c r="H48" t="n">
-        <v>1.04</v>
+        <v>2.06</v>
       </c>
       <c r="I48" t="n">
-        <v>1000</v>
+        <v>2.38</v>
       </c>
       <c r="J48" t="n">
-        <v>1.01</v>
+        <v>3.85</v>
       </c>
       <c r="K48" t="n">
-        <v>740</v>
+        <v>4.6</v>
       </c>
       <c r="L48" t="n">
         <v>0</v>
@@ -12571,10 +12571,10 @@
         <v>0</v>
       </c>
       <c r="P48" t="n">
-        <v>1.04</v>
+        <v>2.26</v>
       </c>
       <c r="Q48" t="n">
-        <v>1.01</v>
+        <v>1.42</v>
       </c>
       <c r="R48" t="n">
         <v>0</v>
@@ -12764,14 +12764,14 @@
       </c>
       <c r="CB48" t="inlineStr">
         <is>
-          <t>2026-05-14 00:34:16</t>
+          <t>2026-05-14 02:53:36</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Swiss Super League</t>
+          <t>Bulgarian A League</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -12786,31 +12786,31 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Winterthur</t>
+          <t>Botev Plovdiv</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Luzern</t>
+          <t>Cherno More</t>
         </is>
       </c>
       <c r="F49" t="n">
-        <v>3.85</v>
+        <v>2.36</v>
       </c>
       <c r="G49" t="n">
-        <v>4.3</v>
+        <v>3.4</v>
       </c>
       <c r="H49" t="n">
-        <v>1.9</v>
+        <v>2.58</v>
       </c>
       <c r="I49" t="n">
-        <v>2.04</v>
+        <v>3.8</v>
       </c>
       <c r="J49" t="n">
-        <v>4</v>
+        <v>2.76</v>
       </c>
       <c r="K49" t="n">
-        <v>4.7</v>
+        <v>5.4</v>
       </c>
       <c r="L49" t="n">
         <v>0</v>
@@ -12825,10 +12825,10 @@
         <v>0</v>
       </c>
       <c r="P49" t="n">
-        <v>3.2</v>
+        <v>1.52</v>
       </c>
       <c r="Q49" t="n">
-        <v>1.35</v>
+        <v>2.08</v>
       </c>
       <c r="R49" t="n">
         <v>0</v>
@@ -13018,14 +13018,14 @@
       </c>
       <c r="CB49" t="inlineStr">
         <is>
-          <t>2026-05-14 00:34:16</t>
+          <t>2026-05-14 02:53:36</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Swiss Super League</t>
+          <t>Bulgarian A League</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -13040,31 +13040,31 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>FC Zurich</t>
+          <t>Arda</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Servette</t>
+          <t>Lokomotiv Plovdiv</t>
         </is>
       </c>
       <c r="F50" t="n">
-        <v>3.15</v>
+        <v>1.65</v>
       </c>
       <c r="G50" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="H50" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="I50" t="n">
+        <v>6</v>
+      </c>
+      <c r="J50" t="n">
         <v>3.95</v>
       </c>
-      <c r="H50" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="I50" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="J50" t="n">
-        <v>3.85</v>
-      </c>
       <c r="K50" t="n">
-        <v>4.6</v>
+        <v>4.4</v>
       </c>
       <c r="L50" t="n">
         <v>0</v>
@@ -13079,10 +13079,10 @@
         <v>0</v>
       </c>
       <c r="P50" t="n">
-        <v>2.26</v>
+        <v>1.78</v>
       </c>
       <c r="Q50" t="n">
-        <v>1.42</v>
+        <v>1.9</v>
       </c>
       <c r="R50" t="n">
         <v>0</v>
@@ -13272,14 +13272,14 @@
       </c>
       <c r="CB50" t="inlineStr">
         <is>
-          <t>2026-05-14 00:34:16</t>
+          <t>2026-05-14 02:53:36</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Swiss Super League</t>
+          <t>Latvian Virsliga</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -13294,31 +13294,31 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Lausanne</t>
+          <t>FK Riga</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Grasshoppers Zurich</t>
+          <t>FK Jelgava</t>
         </is>
       </c>
       <c r="F51" t="n">
-        <v>1.58</v>
+        <v>1.04</v>
       </c>
       <c r="G51" t="n">
-        <v>1.64</v>
+        <v>810</v>
       </c>
       <c r="H51" t="n">
-        <v>5.4</v>
+        <v>1.04</v>
       </c>
       <c r="I51" t="n">
-        <v>6.4</v>
+        <v>940</v>
       </c>
       <c r="J51" t="n">
-        <v>4.2</v>
+        <v>1.02</v>
       </c>
       <c r="K51" t="n">
-        <v>5.1</v>
+        <v>740</v>
       </c>
       <c r="L51" t="n">
         <v>0</v>
@@ -13333,10 +13333,10 @@
         <v>0</v>
       </c>
       <c r="P51" t="n">
-        <v>2.62</v>
+        <v>1.04</v>
       </c>
       <c r="Q51" t="n">
-        <v>1.44</v>
+        <v>1.01</v>
       </c>
       <c r="R51" t="n">
         <v>0</v>
@@ -13526,7 +13526,7 @@
       </c>
       <c r="CB51" t="inlineStr">
         <is>
-          <t>2026-05-14 00:34:16</t>
+          <t>2026-05-14 02:53:36</t>
         </is>
       </c>
     </row>
@@ -13560,10 +13560,10 @@
         <v>1.35</v>
       </c>
       <c r="G52" t="n">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="H52" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="I52" t="n">
         <v>10.5</v>
@@ -13780,7 +13780,7 @@
       </c>
       <c r="CB52" t="inlineStr">
         <is>
-          <t>2026-05-14 00:34:16</t>
+          <t>2026-05-14 02:53:36</t>
         </is>
       </c>
     </row>
@@ -13811,7 +13811,7 @@
         </is>
       </c>
       <c r="F53" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="G53" t="n">
         <v>6</v>
@@ -13820,13 +13820,13 @@
         <v>1.72</v>
       </c>
       <c r="I53" t="n">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="J53" t="n">
         <v>4</v>
       </c>
       <c r="K53" t="n">
-        <v>5.3</v>
+        <v>4.7</v>
       </c>
       <c r="L53" t="n">
         <v>0</v>
@@ -13844,7 +13844,7 @@
         <v>2.3</v>
       </c>
       <c r="Q53" t="n">
-        <v>1.53</v>
+        <v>1.63</v>
       </c>
       <c r="R53" t="n">
         <v>0</v>
@@ -14034,14 +14034,14 @@
       </c>
       <c r="CB53" t="inlineStr">
         <is>
-          <t>2026-05-14 00:34:16</t>
+          <t>2026-05-14 02:53:36</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Croatian HNL</t>
+          <t>Belgian Pro League</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -14056,31 +14056,31 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>Lokomotiva</t>
+          <t>Standard</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Hajduk Split</t>
+          <t>Genk</t>
         </is>
       </c>
       <c r="F54" t="n">
-        <v>3.4</v>
+        <v>3.25</v>
       </c>
       <c r="G54" t="n">
-        <v>5.4</v>
+        <v>3.6</v>
       </c>
       <c r="H54" t="n">
-        <v>1.78</v>
+        <v>2.2</v>
       </c>
       <c r="I54" t="n">
-        <v>2.28</v>
+        <v>2.42</v>
       </c>
       <c r="J54" t="n">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="K54" t="n">
-        <v>5.3</v>
+        <v>3.95</v>
       </c>
       <c r="L54" t="n">
         <v>0</v>
@@ -14095,10 +14095,10 @@
         <v>0</v>
       </c>
       <c r="P54" t="n">
-        <v>1.98</v>
+        <v>2.04</v>
       </c>
       <c r="Q54" t="n">
-        <v>1.61</v>
+        <v>1.79</v>
       </c>
       <c r="R54" t="n">
         <v>0</v>
@@ -14288,14 +14288,14 @@
       </c>
       <c r="CB54" t="inlineStr">
         <is>
-          <t>2026-05-14 00:34:16</t>
+          <t>2026-05-14 02:53:36</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Belgian Pro League</t>
+          <t>Croatian HNL</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -14310,31 +14310,31 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>Standard</t>
+          <t>Lokomotiva</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Genk</t>
+          <t>Hajduk Split</t>
         </is>
       </c>
       <c r="F55" t="n">
-        <v>3.25</v>
+        <v>3.4</v>
       </c>
       <c r="G55" t="n">
-        <v>3.85</v>
+        <v>5.4</v>
       </c>
       <c r="H55" t="n">
-        <v>2.2</v>
+        <v>1.8</v>
       </c>
       <c r="I55" t="n">
-        <v>2.42</v>
+        <v>2.26</v>
       </c>
       <c r="J55" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="K55" t="n">
-        <v>3.95</v>
+        <v>5.3</v>
       </c>
       <c r="L55" t="n">
         <v>0</v>
@@ -14349,10 +14349,10 @@
         <v>0</v>
       </c>
       <c r="P55" t="n">
-        <v>2.04</v>
+        <v>1.98</v>
       </c>
       <c r="Q55" t="n">
-        <v>1.71</v>
+        <v>1.61</v>
       </c>
       <c r="R55" t="n">
         <v>0</v>
@@ -14542,7 +14542,7 @@
       </c>
       <c r="CB55" t="inlineStr">
         <is>
-          <t>2026-05-14 00:34:16</t>
+          <t>2026-05-14 02:53:36</t>
         </is>
       </c>
     </row>
@@ -14564,31 +14564,31 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>Almeria</t>
+          <t>Granada</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Las Palmas</t>
+          <t>Burgos</t>
         </is>
       </c>
       <c r="F56" t="n">
-        <v>2.02</v>
+        <v>3.2</v>
       </c>
       <c r="G56" t="n">
-        <v>2.14</v>
+        <v>3.65</v>
       </c>
       <c r="H56" t="n">
-        <v>3.8</v>
+        <v>2.48</v>
       </c>
       <c r="I56" t="n">
-        <v>4</v>
+        <v>2.72</v>
       </c>
       <c r="J56" t="n">
-        <v>3.7</v>
+        <v>3.05</v>
       </c>
       <c r="K56" t="n">
-        <v>4.1</v>
+        <v>3.25</v>
       </c>
       <c r="L56" t="n">
         <v>0</v>
@@ -14603,10 +14603,10 @@
         <v>0</v>
       </c>
       <c r="P56" t="n">
-        <v>2.14</v>
+        <v>1.54</v>
       </c>
       <c r="Q56" t="n">
-        <v>1.72</v>
+        <v>2.6</v>
       </c>
       <c r="R56" t="n">
         <v>0</v>
@@ -14796,7 +14796,7 @@
       </c>
       <c r="CB56" t="inlineStr">
         <is>
-          <t>2026-05-14 00:34:16</t>
+          <t>2026-05-14 02:53:36</t>
         </is>
       </c>
     </row>
@@ -14818,31 +14818,31 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>Racing Santander</t>
+          <t>Almeria</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Valladolid</t>
+          <t>Las Palmas</t>
         </is>
       </c>
       <c r="F57" t="n">
-        <v>1.47</v>
+        <v>2</v>
       </c>
       <c r="G57" t="n">
-        <v>1.53</v>
+        <v>2.12</v>
       </c>
       <c r="H57" t="n">
-        <v>6.6</v>
+        <v>3.8</v>
       </c>
       <c r="I57" t="n">
-        <v>7.8</v>
+        <v>3.95</v>
       </c>
       <c r="J57" t="n">
-        <v>4.9</v>
+        <v>3.7</v>
       </c>
       <c r="K57" t="n">
-        <v>5.5</v>
+        <v>4.1</v>
       </c>
       <c r="L57" t="n">
         <v>0</v>
@@ -14857,10 +14857,10 @@
         <v>0</v>
       </c>
       <c r="P57" t="n">
-        <v>2.54</v>
+        <v>2.14</v>
       </c>
       <c r="Q57" t="n">
-        <v>1.57</v>
+        <v>1.65</v>
       </c>
       <c r="R57" t="n">
         <v>0</v>
@@ -15050,7 +15050,7 @@
       </c>
       <c r="CB57" t="inlineStr">
         <is>
-          <t>2026-05-14 00:34:16</t>
+          <t>2026-05-14 02:53:36</t>
         </is>
       </c>
     </row>
@@ -15072,31 +15072,31 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>Granada</t>
+          <t>Racing Santander</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Burgos</t>
+          <t>Valladolid</t>
         </is>
       </c>
       <c r="F58" t="n">
-        <v>3.2</v>
+        <v>1.47</v>
       </c>
       <c r="G58" t="n">
-        <v>3.55</v>
+        <v>1.54</v>
       </c>
       <c r="H58" t="n">
-        <v>2.48</v>
+        <v>6.6</v>
       </c>
       <c r="I58" t="n">
-        <v>2.72</v>
+        <v>870</v>
       </c>
       <c r="J58" t="n">
-        <v>3.1</v>
+        <v>4.9</v>
       </c>
       <c r="K58" t="n">
-        <v>3.25</v>
+        <v>950</v>
       </c>
       <c r="L58" t="n">
         <v>0</v>
@@ -15111,10 +15111,10 @@
         <v>0</v>
       </c>
       <c r="P58" t="n">
-        <v>1.54</v>
+        <v>2.54</v>
       </c>
       <c r="Q58" t="n">
-        <v>2.58</v>
+        <v>1.57</v>
       </c>
       <c r="R58" t="n">
         <v>0</v>
@@ -15304,7 +15304,7 @@
       </c>
       <c r="CB58" t="inlineStr">
         <is>
-          <t>2026-05-14 00:34:16</t>
+          <t>2026-05-14 02:53:36</t>
         </is>
       </c>
     </row>
@@ -15326,31 +15326,31 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>Samsunspor</t>
+          <t>Gaziantep FK</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Goztepe</t>
+          <t>Basaksehir</t>
         </is>
       </c>
       <c r="F59" t="n">
-        <v>2.42</v>
+        <v>2.14</v>
       </c>
       <c r="G59" t="n">
-        <v>2.7</v>
+        <v>1000</v>
       </c>
       <c r="H59" t="n">
-        <v>2.86</v>
+        <v>1.04</v>
       </c>
       <c r="I59" t="n">
-        <v>3.25</v>
+        <v>1.91</v>
       </c>
       <c r="J59" t="n">
-        <v>3.6</v>
+        <v>2.14</v>
       </c>
       <c r="K59" t="n">
-        <v>4.3</v>
+        <v>1000</v>
       </c>
       <c r="L59" t="n">
         <v>0</v>
@@ -15365,10 +15365,10 @@
         <v>0</v>
       </c>
       <c r="P59" t="n">
-        <v>2.1</v>
+        <v>1.25</v>
       </c>
       <c r="Q59" t="n">
-        <v>1.63</v>
+        <v>1.01</v>
       </c>
       <c r="R59" t="n">
         <v>0</v>
@@ -15558,7 +15558,7 @@
       </c>
       <c r="CB59" t="inlineStr">
         <is>
-          <t>2026-05-14 00:34:16</t>
+          <t>2026-05-14 02:53:36</t>
         </is>
       </c>
     </row>
@@ -15580,31 +15580,31 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>Gaziantep FK</t>
+          <t>Samsunspor</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Basaksehir</t>
+          <t>Goztepe</t>
         </is>
       </c>
       <c r="F60" t="n">
-        <v>2.1</v>
+        <v>2.42</v>
       </c>
       <c r="G60" t="n">
-        <v>1000</v>
+        <v>2.7</v>
       </c>
       <c r="H60" t="n">
-        <v>1.04</v>
+        <v>2.86</v>
       </c>
       <c r="I60" t="n">
-        <v>1.91</v>
+        <v>3.25</v>
       </c>
       <c r="J60" t="n">
-        <v>2.1</v>
+        <v>3.6</v>
       </c>
       <c r="K60" t="n">
-        <v>1000</v>
+        <v>4.3</v>
       </c>
       <c r="L60" t="n">
         <v>0</v>
@@ -15619,10 +15619,10 @@
         <v>0</v>
       </c>
       <c r="P60" t="n">
-        <v>1.25</v>
+        <v>2.14</v>
       </c>
       <c r="Q60" t="n">
-        <v>1.01</v>
+        <v>1.63</v>
       </c>
       <c r="R60" t="n">
         <v>0</v>
@@ -15812,7 +15812,7 @@
       </c>
       <c r="CB60" t="inlineStr">
         <is>
-          <t>2026-05-14 00:34:16</t>
+          <t>2026-05-14 02:53:36</t>
         </is>
       </c>
     </row>
@@ -16066,7 +16066,7 @@
       </c>
       <c r="CB61" t="inlineStr">
         <is>
-          <t>2026-05-14 00:34:16</t>
+          <t>2026-05-14 02:53:36</t>
         </is>
       </c>
     </row>
@@ -16100,16 +16100,16 @@
         <v>2.04</v>
       </c>
       <c r="G62" t="n">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="H62" t="n">
-        <v>1.09</v>
+        <v>1.8</v>
       </c>
       <c r="I62" t="n">
         <v>2</v>
       </c>
       <c r="J62" t="n">
-        <v>2</v>
+        <v>2.04</v>
       </c>
       <c r="K62" t="n">
         <v>610</v>
@@ -16320,7 +16320,7 @@
       </c>
       <c r="CB62" t="inlineStr">
         <is>
-          <t>2026-05-14 00:34:16</t>
+          <t>2026-05-14 02:53:36</t>
         </is>
       </c>
     </row>
@@ -16351,10 +16351,10 @@
         </is>
       </c>
       <c r="F63" t="n">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="G63" t="n">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="H63" t="n">
         <v>4.9</v>
@@ -16366,7 +16366,7 @@
         <v>3.75</v>
       </c>
       <c r="K63" t="n">
-        <v>4.4</v>
+        <v>4.8</v>
       </c>
       <c r="L63" t="n">
         <v>0</v>
@@ -16381,10 +16381,10 @@
         <v>0</v>
       </c>
       <c r="P63" t="n">
-        <v>1.96</v>
+        <v>1.94</v>
       </c>
       <c r="Q63" t="n">
-        <v>1.85</v>
+        <v>1.73</v>
       </c>
       <c r="R63" t="n">
         <v>0</v>
@@ -16574,7 +16574,7 @@
       </c>
       <c r="CB63" t="inlineStr">
         <is>
-          <t>2026-05-14 00:34:16</t>
+          <t>2026-05-14 02:53:36</t>
         </is>
       </c>
     </row>
@@ -16605,16 +16605,16 @@
         </is>
       </c>
       <c r="F64" t="n">
-        <v>1.96</v>
+        <v>1.93</v>
       </c>
       <c r="G64" t="n">
         <v>2.16</v>
       </c>
       <c r="H64" t="n">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="I64" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="J64" t="n">
         <v>3.45</v>
@@ -16635,7 +16635,7 @@
         <v>0</v>
       </c>
       <c r="P64" t="n">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="Q64" t="n">
         <v>1.91</v>
@@ -16828,14 +16828,14 @@
       </c>
       <c r="CB64" t="inlineStr">
         <is>
-          <t>2026-05-14 00:34:16</t>
+          <t>2026-05-14 02:53:36</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Uruguayan Primera Division</t>
+          <t>Saudi Professional League</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -16850,31 +16850,31 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>Juventud De Las Piedras</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Progreso</t>
+          <t>Al-Kholood Club</t>
         </is>
       </c>
       <c r="F65" t="n">
-        <v>2.04</v>
+        <v>1.28</v>
       </c>
       <c r="G65" t="n">
-        <v>2.28</v>
+        <v>1.35</v>
       </c>
       <c r="H65" t="n">
-        <v>3.7</v>
+        <v>10.5</v>
       </c>
       <c r="I65" t="n">
-        <v>4.5</v>
+        <v>13</v>
       </c>
       <c r="J65" t="n">
-        <v>2.94</v>
+        <v>6</v>
       </c>
       <c r="K65" t="n">
-        <v>4.2</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="L65" t="n">
         <v>0</v>
@@ -16889,10 +16889,10 @@
         <v>0</v>
       </c>
       <c r="P65" t="n">
-        <v>1.7</v>
+        <v>2.68</v>
       </c>
       <c r="Q65" t="n">
-        <v>2.16</v>
+        <v>1.47</v>
       </c>
       <c r="R65" t="n">
         <v>0</v>
@@ -17082,14 +17082,14 @@
       </c>
       <c r="CB65" t="inlineStr">
         <is>
-          <t>2026-05-14 00:34:16</t>
+          <t>2026-05-14 02:53:36</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Saudi Professional League</t>
+          <t>Romanian Liga I</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -17104,31 +17104,31 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Dinamo Bucharest</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Al-Kholood Club</t>
+          <t>CFR Cluj</t>
         </is>
       </c>
       <c r="F66" t="n">
-        <v>1.27</v>
+        <v>2.08</v>
       </c>
       <c r="G66" t="n">
-        <v>1.35</v>
+        <v>2.84</v>
       </c>
       <c r="H66" t="n">
-        <v>10.5</v>
+        <v>2.86</v>
       </c>
       <c r="I66" t="n">
-        <v>13</v>
+        <v>4.4</v>
       </c>
       <c r="J66" t="n">
-        <v>6</v>
+        <v>2.8</v>
       </c>
       <c r="K66" t="n">
-        <v>8.199999999999999</v>
+        <v>5.8</v>
       </c>
       <c r="L66" t="n">
         <v>0</v>
@@ -17143,10 +17143,10 @@
         <v>0</v>
       </c>
       <c r="P66" t="n">
-        <v>2.66</v>
+        <v>1.57</v>
       </c>
       <c r="Q66" t="n">
-        <v>1.47</v>
+        <v>2.12</v>
       </c>
       <c r="R66" t="n">
         <v>0</v>
@@ -17336,14 +17336,14 @@
       </c>
       <c r="CB66" t="inlineStr">
         <is>
-          <t>2026-05-14 00:34:16</t>
+          <t>2026-05-14 02:53:36</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Peruvian Primera Division</t>
+          <t>Uruguayan Primera Division</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -17358,31 +17358,31 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>Melgar</t>
+          <t>Juventud De Las Piedras</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Sport Huancayo</t>
+          <t>Progreso</t>
         </is>
       </c>
       <c r="F67" t="n">
-        <v>1.51</v>
+        <v>2.04</v>
       </c>
       <c r="G67" t="n">
-        <v>1.6</v>
+        <v>2.28</v>
       </c>
       <c r="H67" t="n">
-        <v>5.7</v>
+        <v>3.7</v>
       </c>
       <c r="I67" t="n">
-        <v>7.4</v>
+        <v>4.5</v>
       </c>
       <c r="J67" t="n">
-        <v>4.4</v>
+        <v>2.94</v>
       </c>
       <c r="K67" t="n">
-        <v>5</v>
+        <v>4.2</v>
       </c>
       <c r="L67" t="n">
         <v>0</v>
@@ -17397,11 +17397,11 @@
         <v>0</v>
       </c>
       <c r="P67" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="Q67" t="n">
         <v>2.16</v>
       </c>
-      <c r="Q67" t="n">
-        <v>1.65</v>
-      </c>
       <c r="R67" t="n">
         <v>0</v>
       </c>
@@ -17590,7 +17590,7 @@
       </c>
       <c r="CB67" t="inlineStr">
         <is>
-          <t>2026-05-14 00:34:16</t>
+          <t>2026-05-14 02:53:36</t>
         </is>
       </c>
     </row>
@@ -17844,14 +17844,14 @@
       </c>
       <c r="CB68" t="inlineStr">
         <is>
-          <t>2026-05-14 00:34:16</t>
+          <t>2026-05-14 02:53:36</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Romanian Liga I</t>
+          <t>Peruvian Primera Division</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -17866,31 +17866,31 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>Dinamo Bucharest</t>
+          <t>Melgar</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>CFR Cluj</t>
+          <t>Sport Huancayo</t>
         </is>
       </c>
       <c r="F69" t="n">
-        <v>2.08</v>
+        <v>1.52</v>
       </c>
       <c r="G69" t="n">
-        <v>2.84</v>
+        <v>1.6</v>
       </c>
       <c r="H69" t="n">
-        <v>2.86</v>
+        <v>5.8</v>
       </c>
       <c r="I69" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="J69" t="n">
         <v>4.4</v>
       </c>
-      <c r="J69" t="n">
-        <v>2.8</v>
-      </c>
       <c r="K69" t="n">
-        <v>5.9</v>
+        <v>5</v>
       </c>
       <c r="L69" t="n">
         <v>0</v>
@@ -17905,10 +17905,10 @@
         <v>0</v>
       </c>
       <c r="P69" t="n">
-        <v>1.57</v>
+        <v>2.16</v>
       </c>
       <c r="Q69" t="n">
-        <v>2.12</v>
+        <v>1.65</v>
       </c>
       <c r="R69" t="n">
         <v>0</v>
@@ -18098,7 +18098,7 @@
       </c>
       <c r="CB69" t="inlineStr">
         <is>
-          <t>2026-05-14 00:34:16</t>
+          <t>2026-05-14 02:53:36</t>
         </is>
       </c>
     </row>
@@ -18132,16 +18132,16 @@
         <v>3.65</v>
       </c>
       <c r="G70" t="n">
-        <v>4.6</v>
+        <v>4.4</v>
       </c>
       <c r="H70" t="n">
-        <v>1.94</v>
+        <v>1.93</v>
       </c>
       <c r="I70" t="n">
-        <v>2.16</v>
+        <v>2.1</v>
       </c>
       <c r="J70" t="n">
-        <v>3.55</v>
+        <v>3.95</v>
       </c>
       <c r="K70" t="n">
         <v>4.4</v>
@@ -18352,7 +18352,7 @@
       </c>
       <c r="CB70" t="inlineStr">
         <is>
-          <t>2026-05-14 00:34:16</t>
+          <t>2026-05-14 02:53:36</t>
         </is>
       </c>
     </row>
@@ -18606,7 +18606,7 @@
       </c>
       <c r="CB71" t="inlineStr">
         <is>
-          <t>2026-05-14 00:34:16</t>
+          <t>2026-05-14 02:53:36</t>
         </is>
       </c>
     </row>
@@ -18670,7 +18670,7 @@
         <v>2.36</v>
       </c>
       <c r="Q72" t="n">
-        <v>1.63</v>
+        <v>1.59</v>
       </c>
       <c r="R72" t="n">
         <v>0</v>
@@ -18682,7 +18682,7 @@
         <v>1.62</v>
       </c>
       <c r="U72" t="n">
-        <v>2.4</v>
+        <v>2.42</v>
       </c>
       <c r="V72" t="n">
         <v>0</v>
@@ -18745,10 +18745,10 @@
         <v>34</v>
       </c>
       <c r="AP72" t="n">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="AQ72" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AR72" t="n">
         <v>4.7</v>
@@ -18757,22 +18757,22 @@
         <v>5</v>
       </c>
       <c r="AT72" t="n">
-        <v>11</v>
+        <v>3.95</v>
       </c>
       <c r="AU72" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="AV72" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AW72" t="n">
         <v>4.8</v>
       </c>
       <c r="AX72" t="n">
-        <v>11</v>
+        <v>4.1</v>
       </c>
       <c r="AY72" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AZ72" t="n">
         <v>14.5</v>
@@ -18781,7 +18781,7 @@
         <v>4.8</v>
       </c>
       <c r="BB72" t="n">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="BC72" t="n">
         <v>14.5</v>
@@ -18793,7 +18793,7 @@
         <v>5.1</v>
       </c>
       <c r="BF72" t="n">
-        <v>8.199999999999999</v>
+        <v>3.7</v>
       </c>
       <c r="BG72" t="n">
         <v>4.7</v>
@@ -18860,7 +18860,7 @@
       </c>
       <c r="CB72" t="inlineStr">
         <is>
-          <t>2026-05-14 00:34:16</t>
+          <t>2026-05-14 02:53:36</t>
         </is>
       </c>
     </row>
@@ -18924,7 +18924,7 @@
         <v>1.74</v>
       </c>
       <c r="Q73" t="n">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="R73" t="n">
         <v>0</v>
@@ -19114,7 +19114,7 @@
       </c>
       <c r="CB73" t="inlineStr">
         <is>
-          <t>2026-05-14 00:34:16</t>
+          <t>2026-05-14 02:53:36</t>
         </is>
       </c>
     </row>
@@ -19368,14 +19368,14 @@
       </c>
       <c r="CB74" t="inlineStr">
         <is>
-          <t>2026-05-14 00:34:16</t>
+          <t>2026-05-14 02:53:36</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Paraguayan Primera Division</t>
+          <t>Peruvian Primera Division</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -19390,31 +19390,31 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>Guarani (Par)</t>
+          <t>Juan Pablo II College</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Club Sportivo Ameliano</t>
+          <t>Alianza Atletico</t>
         </is>
       </c>
       <c r="F75" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="G75" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="H75" t="n">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="I75" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="J75" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="K75" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="L75" t="n">
         <v>0</v>
@@ -19429,10 +19429,10 @@
         <v>0</v>
       </c>
       <c r="P75" t="n">
-        <v>1.24</v>
+        <v>1.71</v>
       </c>
       <c r="Q75" t="n">
-        <v>1.01</v>
+        <v>2.06</v>
       </c>
       <c r="R75" t="n">
         <v>0</v>
@@ -19622,14 +19622,14 @@
       </c>
       <c r="CB75" t="inlineStr">
         <is>
-          <t>2026-05-14 00:34:16</t>
+          <t>2026-05-14 02:53:36</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Peruvian Primera Division</t>
+          <t>Paraguayan Primera Division</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -19644,31 +19644,31 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>Juan Pablo II College</t>
+          <t>Guarani (Par)</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Alianza Atletico</t>
+          <t>Club Sportivo Ameliano</t>
         </is>
       </c>
       <c r="F76" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="G76" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="H76" t="n">
-        <v>2.46</v>
+        <v>0</v>
       </c>
       <c r="I76" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="J76" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="K76" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="L76" t="n">
         <v>0</v>
@@ -19683,10 +19683,10 @@
         <v>0</v>
       </c>
       <c r="P76" t="n">
-        <v>1.71</v>
+        <v>1.24</v>
       </c>
       <c r="Q76" t="n">
-        <v>2.06</v>
+        <v>1.01</v>
       </c>
       <c r="R76" t="n">
         <v>0</v>
@@ -19876,14 +19876,14 @@
       </c>
       <c r="CB76" t="inlineStr">
         <is>
-          <t>2026-05-14 00:34:16</t>
+          <t>2026-05-14 02:53:36</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>US MLS</t>
+          <t>Ecuadorian Serie A</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -19893,36 +19893,36 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>17:30:00</t>
+          <t>18:30:00</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>CF Montreal</t>
+          <t>Univ Catolica (Ecu)</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Chicago Fire</t>
+          <t>Delfin</t>
         </is>
       </c>
       <c r="F77" t="n">
-        <v>2.72</v>
+        <v>1.42</v>
       </c>
       <c r="G77" t="n">
-        <v>3.1</v>
+        <v>1.5</v>
       </c>
       <c r="H77" t="n">
-        <v>2.26</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="I77" t="n">
-        <v>2.72</v>
+        <v>12.5</v>
       </c>
       <c r="J77" t="n">
-        <v>1.1</v>
+        <v>4.2</v>
       </c>
       <c r="K77" t="n">
-        <v>4.3</v>
+        <v>5</v>
       </c>
       <c r="L77" t="n">
         <v>0</v>
@@ -19937,10 +19937,10 @@
         <v>0</v>
       </c>
       <c r="P77" t="n">
-        <v>2.34</v>
+        <v>1.72</v>
       </c>
       <c r="Q77" t="n">
-        <v>1.59</v>
+        <v>2.1</v>
       </c>
       <c r="R77" t="n">
         <v>0</v>
@@ -20130,14 +20130,14 @@
       </c>
       <c r="CB77" t="inlineStr">
         <is>
-          <t>2026-05-14 00:34:16</t>
+          <t>2026-05-14 02:53:36</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Chilean Primera Division</t>
+          <t>Uruguayan Primera Division</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -20152,31 +20152,31 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>OHiggins</t>
+          <t>Penarol</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Univ de Concepcion</t>
+          <t>Liverpool Montevideo</t>
         </is>
       </c>
       <c r="F78" t="n">
-        <v>1.79</v>
+        <v>1.72</v>
       </c>
       <c r="G78" t="n">
-        <v>1.95</v>
+        <v>1.92</v>
       </c>
       <c r="H78" t="n">
-        <v>4.4</v>
+        <v>2.12</v>
       </c>
       <c r="I78" t="n">
-        <v>5.8</v>
+        <v>7.2</v>
       </c>
       <c r="J78" t="n">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="K78" t="n">
-        <v>4.7</v>
+        <v>500</v>
       </c>
       <c r="L78" t="n">
         <v>0</v>
@@ -20191,10 +20191,10 @@
         <v>0</v>
       </c>
       <c r="P78" t="n">
-        <v>2.02</v>
+        <v>1.71</v>
       </c>
       <c r="Q78" t="n">
-        <v>1.8</v>
+        <v>2.04</v>
       </c>
       <c r="R78" t="n">
         <v>0</v>
@@ -20384,14 +20384,14 @@
       </c>
       <c r="CB78" t="inlineStr">
         <is>
-          <t>2026-05-14 00:34:16</t>
+          <t>2026-05-14 02:53:36</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Ecuadorian Serie A</t>
+          <t>Chilean Primera Division</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -20406,31 +20406,31 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>Univ Catolica (Ecu)</t>
+          <t>OHiggins</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Delfin</t>
+          <t>Univ de Concepcion</t>
         </is>
       </c>
       <c r="F79" t="n">
-        <v>1.4</v>
+        <v>1.78</v>
       </c>
       <c r="G79" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="H79" t="n">
-        <v>10</v>
+        <v>4.4</v>
       </c>
       <c r="I79" t="n">
-        <v>12.5</v>
+        <v>5.8</v>
       </c>
       <c r="J79" t="n">
-        <v>4.2</v>
+        <v>3.7</v>
       </c>
       <c r="K79" t="n">
-        <v>5</v>
+        <v>4.7</v>
       </c>
       <c r="L79" t="n">
         <v>0</v>
@@ -20445,10 +20445,10 @@
         <v>0</v>
       </c>
       <c r="P79" t="n">
-        <v>1.72</v>
+        <v>2</v>
       </c>
       <c r="Q79" t="n">
-        <v>2.1</v>
+        <v>1.8</v>
       </c>
       <c r="R79" t="n">
         <v>0</v>
@@ -20638,14 +20638,14 @@
       </c>
       <c r="CB79" t="inlineStr">
         <is>
-          <t>2026-05-14 00:34:16</t>
+          <t>2026-05-14 02:53:36</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Uruguayan Primera Division</t>
+          <t>Peruvian Primera Division</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -20655,36 +20655,36 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>18:30:00</t>
+          <t>19:45:00</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>Penarol</t>
+          <t>Cienciano</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Liverpool Montevideo</t>
+          <t>Alianza Lima</t>
         </is>
       </c>
       <c r="F80" t="n">
-        <v>1.09</v>
+        <v>2.14</v>
       </c>
       <c r="G80" t="n">
-        <v>1.92</v>
+        <v>2.5</v>
       </c>
       <c r="H80" t="n">
-        <v>2.08</v>
+        <v>3.35</v>
       </c>
       <c r="I80" t="n">
-        <v>870</v>
+        <v>4.1</v>
       </c>
       <c r="J80" t="n">
-        <v>2.08</v>
+        <v>3.1</v>
       </c>
       <c r="K80" t="n">
-        <v>500</v>
+        <v>3.75</v>
       </c>
       <c r="L80" t="n">
         <v>0</v>
@@ -20699,10 +20699,10 @@
         <v>0</v>
       </c>
       <c r="P80" t="n">
-        <v>1.25</v>
+        <v>1.71</v>
       </c>
       <c r="Q80" t="n">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="R80" t="n">
         <v>0</v>
@@ -20892,1785 +20892,7 @@
       </c>
       <c r="CB80" t="inlineStr">
         <is>
-          <t>2026-05-14 00:34:16</t>
-        </is>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" t="inlineStr">
-        <is>
-          <t>Peruvian Primera Division</t>
-        </is>
-      </c>
-      <c r="B81" t="inlineStr">
-        <is>
-          <t>2026-05-16</t>
-        </is>
-      </c>
-      <c r="C81" t="inlineStr">
-        <is>
-          <t>19:45:00</t>
-        </is>
-      </c>
-      <c r="D81" t="inlineStr">
-        <is>
-          <t>Cienciano</t>
-        </is>
-      </c>
-      <c r="E81" t="inlineStr">
-        <is>
-          <t>Alianza Lima</t>
-        </is>
-      </c>
-      <c r="F81" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="G81" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="H81" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="I81" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="J81" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="K81" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="L81" t="n">
-        <v>0</v>
-      </c>
-      <c r="M81" t="n">
-        <v>0</v>
-      </c>
-      <c r="N81" t="n">
-        <v>0</v>
-      </c>
-      <c r="O81" t="n">
-        <v>0</v>
-      </c>
-      <c r="P81" t="n">
-        <v>1.69</v>
-      </c>
-      <c r="Q81" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="R81" t="n">
-        <v>0</v>
-      </c>
-      <c r="S81" t="n">
-        <v>0</v>
-      </c>
-      <c r="T81" t="n">
-        <v>0</v>
-      </c>
-      <c r="U81" t="n">
-        <v>0</v>
-      </c>
-      <c r="V81" t="n">
-        <v>0</v>
-      </c>
-      <c r="W81" t="n">
-        <v>0</v>
-      </c>
-      <c r="X81" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y81" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z81" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA81" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB81" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC81" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD81" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE81" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF81" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG81" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH81" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI81" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ81" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK81" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL81" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM81" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN81" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO81" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP81" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ81" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR81" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS81" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT81" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU81" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV81" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW81" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX81" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY81" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ81" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA81" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB81" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC81" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD81" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE81" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF81" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG81" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH81" t="n">
-        <v>0</v>
-      </c>
-      <c r="BI81" t="n">
-        <v>0</v>
-      </c>
-      <c r="BJ81" t="n">
-        <v>0</v>
-      </c>
-      <c r="BK81" t="n">
-        <v>0</v>
-      </c>
-      <c r="BL81" t="n">
-        <v>0</v>
-      </c>
-      <c r="BM81" t="n">
-        <v>0</v>
-      </c>
-      <c r="BN81" t="n">
-        <v>0</v>
-      </c>
-      <c r="BO81" t="n">
-        <v>0</v>
-      </c>
-      <c r="BP81" t="n">
-        <v>0</v>
-      </c>
-      <c r="BQ81" t="n">
-        <v>0</v>
-      </c>
-      <c r="BR81" t="n">
-        <v>0</v>
-      </c>
-      <c r="BS81" t="n">
-        <v>0</v>
-      </c>
-      <c r="BT81" t="n">
-        <v>0</v>
-      </c>
-      <c r="BU81" t="n">
-        <v>0</v>
-      </c>
-      <c r="BV81" t="n">
-        <v>0</v>
-      </c>
-      <c r="BW81" t="n">
-        <v>0</v>
-      </c>
-      <c r="BX81" t="n">
-        <v>0</v>
-      </c>
-      <c r="BY81" t="n">
-        <v>0</v>
-      </c>
-      <c r="BZ81" t="n">
-        <v>0</v>
-      </c>
-      <c r="CA81" t="n">
-        <v>0</v>
-      </c>
-      <c r="CB81" t="inlineStr">
-        <is>
-          <t>2026-05-14 00:34:16</t>
-        </is>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" t="inlineStr">
-        <is>
-          <t>US MLS</t>
-        </is>
-      </c>
-      <c r="B82" t="inlineStr">
-        <is>
-          <t>2026-05-16</t>
-        </is>
-      </c>
-      <c r="C82" t="inlineStr">
-        <is>
-          <t>20:30:00</t>
-        </is>
-      </c>
-      <c r="D82" t="inlineStr">
-        <is>
-          <t>Orlando City</t>
-        </is>
-      </c>
-      <c r="E82" t="inlineStr">
-        <is>
-          <t>Atlanta Utd</t>
-        </is>
-      </c>
-      <c r="F82" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="G82" t="n">
-        <v>2.54</v>
-      </c>
-      <c r="H82" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="I82" t="n">
-        <v>1000</v>
-      </c>
-      <c r="J82" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="K82" t="n">
-        <v>1000</v>
-      </c>
-      <c r="L82" t="n">
-        <v>0</v>
-      </c>
-      <c r="M82" t="n">
-        <v>0</v>
-      </c>
-      <c r="N82" t="n">
-        <v>0</v>
-      </c>
-      <c r="O82" t="n">
-        <v>0</v>
-      </c>
-      <c r="P82" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="Q82" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="R82" t="n">
-        <v>0</v>
-      </c>
-      <c r="S82" t="n">
-        <v>0</v>
-      </c>
-      <c r="T82" t="n">
-        <v>0</v>
-      </c>
-      <c r="U82" t="n">
-        <v>0</v>
-      </c>
-      <c r="V82" t="n">
-        <v>0</v>
-      </c>
-      <c r="W82" t="n">
-        <v>0</v>
-      </c>
-      <c r="X82" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y82" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z82" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA82" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB82" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC82" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD82" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE82" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF82" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG82" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH82" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI82" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ82" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK82" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL82" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM82" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN82" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO82" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP82" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ82" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR82" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS82" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT82" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU82" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV82" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW82" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX82" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY82" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ82" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA82" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB82" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC82" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD82" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE82" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF82" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG82" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH82" t="n">
-        <v>0</v>
-      </c>
-      <c r="BI82" t="n">
-        <v>0</v>
-      </c>
-      <c r="BJ82" t="n">
-        <v>0</v>
-      </c>
-      <c r="BK82" t="n">
-        <v>0</v>
-      </c>
-      <c r="BL82" t="n">
-        <v>0</v>
-      </c>
-      <c r="BM82" t="n">
-        <v>0</v>
-      </c>
-      <c r="BN82" t="n">
-        <v>0</v>
-      </c>
-      <c r="BO82" t="n">
-        <v>0</v>
-      </c>
-      <c r="BP82" t="n">
-        <v>0</v>
-      </c>
-      <c r="BQ82" t="n">
-        <v>0</v>
-      </c>
-      <c r="BR82" t="n">
-        <v>0</v>
-      </c>
-      <c r="BS82" t="n">
-        <v>0</v>
-      </c>
-      <c r="BT82" t="n">
-        <v>0</v>
-      </c>
-      <c r="BU82" t="n">
-        <v>0</v>
-      </c>
-      <c r="BV82" t="n">
-        <v>0</v>
-      </c>
-      <c r="BW82" t="n">
-        <v>0</v>
-      </c>
-      <c r="BX82" t="n">
-        <v>0</v>
-      </c>
-      <c r="BY82" t="n">
-        <v>0</v>
-      </c>
-      <c r="BZ82" t="n">
-        <v>0</v>
-      </c>
-      <c r="CA82" t="n">
-        <v>0</v>
-      </c>
-      <c r="CB82" t="inlineStr">
-        <is>
-          <t>2026-05-14 00:34:16</t>
-        </is>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" t="inlineStr">
-        <is>
-          <t>US MLS</t>
-        </is>
-      </c>
-      <c r="B83" t="inlineStr">
-        <is>
-          <t>2026-05-16</t>
-        </is>
-      </c>
-      <c r="C83" t="inlineStr">
-        <is>
-          <t>20:30:00</t>
-        </is>
-      </c>
-      <c r="D83" t="inlineStr">
-        <is>
-          <t>Charlotte FC</t>
-        </is>
-      </c>
-      <c r="E83" t="inlineStr">
-        <is>
-          <t>Toronto FC</t>
-        </is>
-      </c>
-      <c r="F83" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="G83" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="H83" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="I83" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="J83" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="K83" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="L83" t="n">
-        <v>0</v>
-      </c>
-      <c r="M83" t="n">
-        <v>0</v>
-      </c>
-      <c r="N83" t="n">
-        <v>0</v>
-      </c>
-      <c r="O83" t="n">
-        <v>0</v>
-      </c>
-      <c r="P83" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="Q83" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="R83" t="n">
-        <v>0</v>
-      </c>
-      <c r="S83" t="n">
-        <v>0</v>
-      </c>
-      <c r="T83" t="n">
-        <v>0</v>
-      </c>
-      <c r="U83" t="n">
-        <v>0</v>
-      </c>
-      <c r="V83" t="n">
-        <v>0</v>
-      </c>
-      <c r="W83" t="n">
-        <v>0</v>
-      </c>
-      <c r="X83" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y83" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z83" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA83" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB83" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC83" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD83" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE83" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF83" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG83" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH83" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI83" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ83" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK83" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL83" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM83" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN83" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO83" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP83" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ83" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR83" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS83" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT83" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU83" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV83" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW83" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX83" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY83" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ83" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA83" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB83" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC83" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD83" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE83" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF83" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG83" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH83" t="n">
-        <v>0</v>
-      </c>
-      <c r="BI83" t="n">
-        <v>0</v>
-      </c>
-      <c r="BJ83" t="n">
-        <v>0</v>
-      </c>
-      <c r="BK83" t="n">
-        <v>0</v>
-      </c>
-      <c r="BL83" t="n">
-        <v>0</v>
-      </c>
-      <c r="BM83" t="n">
-        <v>0</v>
-      </c>
-      <c r="BN83" t="n">
-        <v>0</v>
-      </c>
-      <c r="BO83" t="n">
-        <v>0</v>
-      </c>
-      <c r="BP83" t="n">
-        <v>0</v>
-      </c>
-      <c r="BQ83" t="n">
-        <v>0</v>
-      </c>
-      <c r="BR83" t="n">
-        <v>0</v>
-      </c>
-      <c r="BS83" t="n">
-        <v>0</v>
-      </c>
-      <c r="BT83" t="n">
-        <v>0</v>
-      </c>
-      <c r="BU83" t="n">
-        <v>0</v>
-      </c>
-      <c r="BV83" t="n">
-        <v>0</v>
-      </c>
-      <c r="BW83" t="n">
-        <v>0</v>
-      </c>
-      <c r="BX83" t="n">
-        <v>0</v>
-      </c>
-      <c r="BY83" t="n">
-        <v>0</v>
-      </c>
-      <c r="BZ83" t="n">
-        <v>0</v>
-      </c>
-      <c r="CA83" t="n">
-        <v>0</v>
-      </c>
-      <c r="CB83" t="inlineStr">
-        <is>
-          <t>2026-05-14 00:34:16</t>
-        </is>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" t="inlineStr">
-        <is>
-          <t>US MLS</t>
-        </is>
-      </c>
-      <c r="B84" t="inlineStr">
-        <is>
-          <t>2026-05-16</t>
-        </is>
-      </c>
-      <c r="C84" t="inlineStr">
-        <is>
-          <t>20:30:00</t>
-        </is>
-      </c>
-      <c r="D84" t="inlineStr">
-        <is>
-          <t>New York Red Bulls</t>
-        </is>
-      </c>
-      <c r="E84" t="inlineStr">
-        <is>
-          <t>New York City</t>
-        </is>
-      </c>
-      <c r="F84" t="n">
-        <v>2.42</v>
-      </c>
-      <c r="G84" t="n">
-        <v>2.54</v>
-      </c>
-      <c r="H84" t="n">
-        <v>2.76</v>
-      </c>
-      <c r="I84" t="n">
-        <v>2.86</v>
-      </c>
-      <c r="J84" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="K84" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="L84" t="n">
-        <v>0</v>
-      </c>
-      <c r="M84" t="n">
-        <v>0</v>
-      </c>
-      <c r="N84" t="n">
-        <v>0</v>
-      </c>
-      <c r="O84" t="n">
-        <v>0</v>
-      </c>
-      <c r="P84" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="Q84" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="R84" t="n">
-        <v>0</v>
-      </c>
-      <c r="S84" t="n">
-        <v>0</v>
-      </c>
-      <c r="T84" t="n">
-        <v>0</v>
-      </c>
-      <c r="U84" t="n">
-        <v>0</v>
-      </c>
-      <c r="V84" t="n">
-        <v>0</v>
-      </c>
-      <c r="W84" t="n">
-        <v>0</v>
-      </c>
-      <c r="X84" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y84" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z84" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA84" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB84" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC84" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD84" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE84" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF84" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG84" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH84" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI84" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ84" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK84" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL84" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM84" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN84" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO84" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP84" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ84" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR84" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS84" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT84" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU84" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV84" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW84" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX84" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY84" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ84" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA84" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB84" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC84" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD84" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE84" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF84" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG84" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH84" t="n">
-        <v>0</v>
-      </c>
-      <c r="BI84" t="n">
-        <v>0</v>
-      </c>
-      <c r="BJ84" t="n">
-        <v>0</v>
-      </c>
-      <c r="BK84" t="n">
-        <v>0</v>
-      </c>
-      <c r="BL84" t="n">
-        <v>0</v>
-      </c>
-      <c r="BM84" t="n">
-        <v>0</v>
-      </c>
-      <c r="BN84" t="n">
-        <v>0</v>
-      </c>
-      <c r="BO84" t="n">
-        <v>0</v>
-      </c>
-      <c r="BP84" t="n">
-        <v>0</v>
-      </c>
-      <c r="BQ84" t="n">
-        <v>0</v>
-      </c>
-      <c r="BR84" t="n">
-        <v>0</v>
-      </c>
-      <c r="BS84" t="n">
-        <v>0</v>
-      </c>
-      <c r="BT84" t="n">
-        <v>0</v>
-      </c>
-      <c r="BU84" t="n">
-        <v>0</v>
-      </c>
-      <c r="BV84" t="n">
-        <v>0</v>
-      </c>
-      <c r="BW84" t="n">
-        <v>0</v>
-      </c>
-      <c r="BX84" t="n">
-        <v>0</v>
-      </c>
-      <c r="BY84" t="n">
-        <v>0</v>
-      </c>
-      <c r="BZ84" t="n">
-        <v>0</v>
-      </c>
-      <c r="CA84" t="n">
-        <v>0</v>
-      </c>
-      <c r="CB84" t="inlineStr">
-        <is>
-          <t>2026-05-14 00:34:16</t>
-        </is>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" t="inlineStr">
-        <is>
-          <t>US MLS</t>
-        </is>
-      </c>
-      <c r="B85" t="inlineStr">
-        <is>
-          <t>2026-05-16</t>
-        </is>
-      </c>
-      <c r="C85" t="inlineStr">
-        <is>
-          <t>20:30:00</t>
-        </is>
-      </c>
-      <c r="D85" t="inlineStr">
-        <is>
-          <t>Philadelphia</t>
-        </is>
-      </c>
-      <c r="E85" t="inlineStr">
-        <is>
-          <t>Columbus</t>
-        </is>
-      </c>
-      <c r="F85" t="n">
-        <v>2.24</v>
-      </c>
-      <c r="G85" t="n">
-        <v>2.42</v>
-      </c>
-      <c r="H85" t="n">
-        <v>2.96</v>
-      </c>
-      <c r="I85" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="J85" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="K85" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="L85" t="n">
-        <v>0</v>
-      </c>
-      <c r="M85" t="n">
-        <v>0</v>
-      </c>
-      <c r="N85" t="n">
-        <v>0</v>
-      </c>
-      <c r="O85" t="n">
-        <v>0</v>
-      </c>
-      <c r="P85" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="Q85" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="R85" t="n">
-        <v>0</v>
-      </c>
-      <c r="S85" t="n">
-        <v>0</v>
-      </c>
-      <c r="T85" t="n">
-        <v>0</v>
-      </c>
-      <c r="U85" t="n">
-        <v>0</v>
-      </c>
-      <c r="V85" t="n">
-        <v>0</v>
-      </c>
-      <c r="W85" t="n">
-        <v>0</v>
-      </c>
-      <c r="X85" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y85" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z85" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA85" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB85" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC85" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD85" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE85" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF85" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG85" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH85" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI85" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ85" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK85" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL85" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM85" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN85" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO85" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP85" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ85" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR85" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS85" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT85" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU85" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV85" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW85" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX85" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY85" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ85" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA85" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB85" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC85" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD85" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE85" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF85" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG85" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH85" t="n">
-        <v>0</v>
-      </c>
-      <c r="BI85" t="n">
-        <v>0</v>
-      </c>
-      <c r="BJ85" t="n">
-        <v>0</v>
-      </c>
-      <c r="BK85" t="n">
-        <v>0</v>
-      </c>
-      <c r="BL85" t="n">
-        <v>0</v>
-      </c>
-      <c r="BM85" t="n">
-        <v>0</v>
-      </c>
-      <c r="BN85" t="n">
-        <v>0</v>
-      </c>
-      <c r="BO85" t="n">
-        <v>0</v>
-      </c>
-      <c r="BP85" t="n">
-        <v>0</v>
-      </c>
-      <c r="BQ85" t="n">
-        <v>0</v>
-      </c>
-      <c r="BR85" t="n">
-        <v>0</v>
-      </c>
-      <c r="BS85" t="n">
-        <v>0</v>
-      </c>
-      <c r="BT85" t="n">
-        <v>0</v>
-      </c>
-      <c r="BU85" t="n">
-        <v>0</v>
-      </c>
-      <c r="BV85" t="n">
-        <v>0</v>
-      </c>
-      <c r="BW85" t="n">
-        <v>0</v>
-      </c>
-      <c r="BX85" t="n">
-        <v>0</v>
-      </c>
-      <c r="BY85" t="n">
-        <v>0</v>
-      </c>
-      <c r="BZ85" t="n">
-        <v>0</v>
-      </c>
-      <c r="CA85" t="n">
-        <v>0</v>
-      </c>
-      <c r="CB85" t="inlineStr">
-        <is>
-          <t>2026-05-14 00:34:16</t>
-        </is>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" t="inlineStr">
-        <is>
-          <t>US MLS</t>
-        </is>
-      </c>
-      <c r="B86" t="inlineStr">
-        <is>
-          <t>2026-05-16</t>
-        </is>
-      </c>
-      <c r="C86" t="inlineStr">
-        <is>
-          <t>20:30:00</t>
-        </is>
-      </c>
-      <c r="D86" t="inlineStr">
-        <is>
-          <t>New England</t>
-        </is>
-      </c>
-      <c r="E86" t="inlineStr">
-        <is>
-          <t>Minnesota Utd</t>
-        </is>
-      </c>
-      <c r="F86" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="G86" t="n">
-        <v>2.34</v>
-      </c>
-      <c r="H86" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="I86" t="n">
-        <v>1000</v>
-      </c>
-      <c r="J86" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="K86" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="L86" t="n">
-        <v>0</v>
-      </c>
-      <c r="M86" t="n">
-        <v>0</v>
-      </c>
-      <c r="N86" t="n">
-        <v>0</v>
-      </c>
-      <c r="O86" t="n">
-        <v>0</v>
-      </c>
-      <c r="P86" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="Q86" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="R86" t="n">
-        <v>0</v>
-      </c>
-      <c r="S86" t="n">
-        <v>0</v>
-      </c>
-      <c r="T86" t="n">
-        <v>0</v>
-      </c>
-      <c r="U86" t="n">
-        <v>0</v>
-      </c>
-      <c r="V86" t="n">
-        <v>0</v>
-      </c>
-      <c r="W86" t="n">
-        <v>0</v>
-      </c>
-      <c r="X86" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y86" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z86" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA86" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB86" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC86" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD86" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE86" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF86" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG86" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH86" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI86" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ86" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK86" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL86" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM86" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN86" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO86" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP86" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ86" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR86" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS86" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT86" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU86" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV86" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW86" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX86" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY86" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ86" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA86" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB86" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC86" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD86" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE86" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF86" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG86" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH86" t="n">
-        <v>0</v>
-      </c>
-      <c r="BI86" t="n">
-        <v>0</v>
-      </c>
-      <c r="BJ86" t="n">
-        <v>0</v>
-      </c>
-      <c r="BK86" t="n">
-        <v>0</v>
-      </c>
-      <c r="BL86" t="n">
-        <v>0</v>
-      </c>
-      <c r="BM86" t="n">
-        <v>0</v>
-      </c>
-      <c r="BN86" t="n">
-        <v>0</v>
-      </c>
-      <c r="BO86" t="n">
-        <v>0</v>
-      </c>
-      <c r="BP86" t="n">
-        <v>0</v>
-      </c>
-      <c r="BQ86" t="n">
-        <v>0</v>
-      </c>
-      <c r="BR86" t="n">
-        <v>0</v>
-      </c>
-      <c r="BS86" t="n">
-        <v>0</v>
-      </c>
-      <c r="BT86" t="n">
-        <v>0</v>
-      </c>
-      <c r="BU86" t="n">
-        <v>0</v>
-      </c>
-      <c r="BV86" t="n">
-        <v>0</v>
-      </c>
-      <c r="BW86" t="n">
-        <v>0</v>
-      </c>
-      <c r="BX86" t="n">
-        <v>0</v>
-      </c>
-      <c r="BY86" t="n">
-        <v>0</v>
-      </c>
-      <c r="BZ86" t="n">
-        <v>0</v>
-      </c>
-      <c r="CA86" t="n">
-        <v>0</v>
-      </c>
-      <c r="CB86" t="inlineStr">
-        <is>
-          <t>2026-05-14 00:34:16</t>
-        </is>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" t="inlineStr">
-        <is>
-          <t>US MLS</t>
-        </is>
-      </c>
-      <c r="B87" t="inlineStr">
-        <is>
-          <t>2026-05-16</t>
-        </is>
-      </c>
-      <c r="C87" t="inlineStr">
-        <is>
-          <t>20:30:00</t>
-        </is>
-      </c>
-      <c r="D87" t="inlineStr">
-        <is>
-          <t>DC Utd</t>
-        </is>
-      </c>
-      <c r="E87" t="inlineStr">
-        <is>
-          <t>St Louis City SC</t>
-        </is>
-      </c>
-      <c r="F87" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="G87" t="n">
-        <v>2.94</v>
-      </c>
-      <c r="H87" t="n">
-        <v>2.22</v>
-      </c>
-      <c r="I87" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="J87" t="n">
-        <v>2.58</v>
-      </c>
-      <c r="K87" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="L87" t="n">
-        <v>0</v>
-      </c>
-      <c r="M87" t="n">
-        <v>0</v>
-      </c>
-      <c r="N87" t="n">
-        <v>0</v>
-      </c>
-      <c r="O87" t="n">
-        <v>0</v>
-      </c>
-      <c r="P87" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="Q87" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="R87" t="n">
-        <v>0</v>
-      </c>
-      <c r="S87" t="n">
-        <v>0</v>
-      </c>
-      <c r="T87" t="n">
-        <v>0</v>
-      </c>
-      <c r="U87" t="n">
-        <v>0</v>
-      </c>
-      <c r="V87" t="n">
-        <v>0</v>
-      </c>
-      <c r="W87" t="n">
-        <v>0</v>
-      </c>
-      <c r="X87" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y87" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z87" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA87" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB87" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC87" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD87" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE87" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF87" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG87" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH87" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI87" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ87" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK87" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL87" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM87" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN87" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO87" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP87" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ87" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR87" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS87" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT87" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU87" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV87" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW87" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX87" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY87" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ87" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA87" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB87" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC87" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD87" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE87" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF87" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG87" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH87" t="n">
-        <v>0</v>
-      </c>
-      <c r="BI87" t="n">
-        <v>0</v>
-      </c>
-      <c r="BJ87" t="n">
-        <v>0</v>
-      </c>
-      <c r="BK87" t="n">
-        <v>0</v>
-      </c>
-      <c r="BL87" t="n">
-        <v>0</v>
-      </c>
-      <c r="BM87" t="n">
-        <v>0</v>
-      </c>
-      <c r="BN87" t="n">
-        <v>0</v>
-      </c>
-      <c r="BO87" t="n">
-        <v>0</v>
-      </c>
-      <c r="BP87" t="n">
-        <v>0</v>
-      </c>
-      <c r="BQ87" t="n">
-        <v>0</v>
-      </c>
-      <c r="BR87" t="n">
-        <v>0</v>
-      </c>
-      <c r="BS87" t="n">
-        <v>0</v>
-      </c>
-      <c r="BT87" t="n">
-        <v>0</v>
-      </c>
-      <c r="BU87" t="n">
-        <v>0</v>
-      </c>
-      <c r="BV87" t="n">
-        <v>0</v>
-      </c>
-      <c r="BW87" t="n">
-        <v>0</v>
-      </c>
-      <c r="BX87" t="n">
-        <v>0</v>
-      </c>
-      <c r="BY87" t="n">
-        <v>0</v>
-      </c>
-      <c r="BZ87" t="n">
-        <v>0</v>
-      </c>
-      <c r="CA87" t="n">
-        <v>0</v>
-      </c>
-      <c r="CB87" t="inlineStr">
-        <is>
-          <t>2026-05-14 00:34:16</t>
+          <t>2026-05-14 02:53:36</t>
         </is>
       </c>
     </row>
